--- a/03-tool/offline/baseline-assessment.xlsx
+++ b/03-tool/offline/baseline-assessment.xlsx
@@ -2144,7 +2144,7 @@
     <t>文档链接</t>
   </si>
   <si>
-    <t>https://claude.ai/code/artifact/a89875c9-b306-4067-b517-e3a093231b20</t>
+    <t>https://github.com/teloa-ai/agent-baseline-assessor/blob/main/01-standard/zh-CN/baseline-v1.0.md</t>
   </si>
   <si>
     <t>内容</t>

--- a/03-tool/offline/baseline-assessment.xlsx
+++ b/03-tool/offline/baseline-assessment.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="评估表" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="汇总" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="差距清单" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="架构视角" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="说明" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Assessment Sheet" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Summary" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Gap List" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Architecture View" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Notes" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'评估表'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assessment Sheet'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,22 +20,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5642" uniqueCount="727">
   <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>章</t>
-  </si>
-  <si>
-    <t>小节</t>
-  </si>
-  <si>
-    <t>落点组件</t>
-  </si>
-  <si>
-    <t>要求</t>
-  </si>
-  <si>
-    <t>最低等级</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Chapter</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Enforcement Component</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Minimum level</t>
   </si>
   <si>
     <t>L1</t>
@@ -47,46 +47,46 @@
     <t>L3</t>
   </si>
   <si>
-    <t>适用条件</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>证据与说明</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>计划完成</t>
-  </si>
-  <si>
-    <t>等级序号</t>
+    <t>Applicability</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Evidence and Notes</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Planned Completion</t>
+  </si>
+  <si>
+    <t>Level No.</t>
   </si>
   <si>
     <t>V1.1.1</t>
   </si>
   <si>
-    <t>V1 身份与认证</t>
-  </si>
-  <si>
-    <t>V1.1 用户认证</t>
-  </si>
-  <si>
-    <t>身份层</t>
-  </si>
-  <si>
-    <t>平台及其全部渠道应只允许通过企业 IdP（OIDC 或 SAML）登录，不提供独立的本地账号，V10.5 规定的紧急访问账号除外</t>
+    <t>V1 Identity and Authentication</t>
+  </si>
+  <si>
+    <t>V1.1 User Authentication</t>
+  </si>
+  <si>
+    <t>Identity layer</t>
+  </si>
+  <si>
+    <t>The platform and all its channels shall allow login only through the enterprise IdP (OIDC or SAML) and shall not provide independent local accounts, except for the break-glass accounts specified in V10.5</t>
   </si>
   <si>
     <t>✓</t>
   </si>
   <si>
-    <t>所有平台</t>
-  </si>
-  <si>
-    <t>未评估</t>
+    <t>All platforms</t>
+  </si>
+  <si>
+    <t>Not assessed</t>
   </si>
   <si>
     <t/>
@@ -95,112 +95,112 @@
     <t>V1.1.2</t>
   </si>
   <si>
-    <t>应通过 SCIM 或等效机制同步用户和组，IdP 中禁用的用户在平台中同步禁用</t>
+    <t>Users and groups shall be synchronized through SCIM or an equivalent mechanism, and users disabled in the IdP shall be disabled in the platform in sync</t>
   </si>
   <si>
     <t>V1.1.3</t>
   </si>
   <si>
-    <t>应在用户会话中保留 IdP 签发的认证时间和认证强度，供 V3.5 的二次认证判断使用</t>
+    <t>The authentication time and authentication strength issued by the IdP shall be retained in the user session for use in the step-up authentication decisions of V3.5</t>
   </si>
   <si>
     <t>V1.1.4</t>
   </si>
   <si>
-    <t>通过 API 调用 Agent 的凭证（如 API Key、个人访问令牌）应绑定到企业 IdP 中的具体用户或非人类身份，设置到期时间和权限范围，身份禁用时同步失效</t>
+    <t>Credentials used to invoke agents through an API (such as API keys and personal access tokens) shall be bound to a specific user or non-human identity in the enterprise IdP, shall have an expiration time and a permission scope set, and shall be revoked automatically when the identity is disabled</t>
   </si>
   <si>
     <t>V1.2.1</t>
   </si>
   <si>
-    <t>V1.2 渠道身份映射</t>
-  </si>
-  <si>
-    <t>交互渠道</t>
-  </si>
-  <si>
-    <t>渠道账号应先通过一次 SSO 登录与企业身份绑定，才能调用 Agent</t>
-  </si>
-  <si>
-    <t>支持 IM、邮件、浏览器插件等第三方渠道的平台</t>
+    <t>V1.2 Channel Identity Mapping</t>
+  </si>
+  <si>
+    <t>Interaction channel</t>
+  </si>
+  <si>
+    <t>A channel account shall be bound to an enterprise identity through a one-time SSO login before it can invoke an agent</t>
+  </si>
+  <si>
+    <t>Platforms that support third-party channels such as IM, email, and browser extensions</t>
   </si>
   <si>
     <t>V1.2.2</t>
   </si>
   <si>
-    <t>应以 SSO 绑定结果作为渠道账号的唯一身份依据，不按昵称、显示名或邮箱字符串匹配；邮件渠道按 V1.2.6 执行</t>
+    <t>The SSO binding result shall be the sole basis for identifying a channel account. Matching by nickname, display name, or email string is not permitted. The email channel follows V1.2.6.</t>
   </si>
   <si>
     <t>V1.2.3</t>
   </si>
   <si>
-    <t>IdP 禁用用户后，该用户的全部渠道绑定应同步失效</t>
+    <t>When a user is disabled in the IdP, all of that user's channel bindings shall be invalidated in sync</t>
   </si>
   <si>
     <t>V1.2.4</t>
   </si>
   <si>
-    <t>应识别外部访客和跨组织共享频道中的账号，并为其单独限定可用的 Agent 和能力</t>
+    <t>Accounts from external visitors and from cross-organization shared channels shall be identified, and the agents and capabilities available to them shall be restricted separately</t>
   </si>
   <si>
     <t>V1.2.5</t>
   </si>
   <si>
-    <t>在渠道内触发高风险操作时，应要求用户通过企业 IdP 完成二次认证</t>
+    <t>When a high-risk operation is triggered within a channel, the user shall be required to complete step-up authentication through the enterprise IdP</t>
   </si>
   <si>
     <t>V1.2.6</t>
   </si>
   <si>
-    <t>邮件渠道应只受理通过 DMARC 校验的邮件（SPF 或 DKIM 通过且与发件域对齐），外部域的发件人不能触发代表用户的操作</t>
+    <t>The email channel shall accept only email that passes DMARC verification (SPF or DKIM passing and aligned with the From domain). Senders from external domains shall not be able to trigger operations on behalf of a user.</t>
   </si>
   <si>
     <t>V1.3.1</t>
   </si>
   <si>
-    <t>V1.3 Agent 身份</t>
-  </si>
-  <si>
-    <t>每个 Agent 应有平台签发的唯一身份标识，不采信 Agent 自报的身份</t>
+    <t>V1.3 Agent Identity</t>
+  </si>
+  <si>
+    <t>Each agent shall have a unique identifier issued by the platform. The platform shall not accept identities self-reported by the agent.</t>
   </si>
   <si>
     <t>V1.3.2</t>
   </si>
   <si>
-    <t>应为自主 Agent 在企业目录中建立独立的非人类身份，不使用任何员工的个人账号</t>
+    <t>An independent non-human identity shall be established in the enterprise directory for each autonomous agent. No employee's personal account shall be used.</t>
   </si>
   <si>
     <t>V1.3.3</t>
   </si>
   <si>
-    <t>下游系统</t>
-  </si>
-  <si>
-    <t>自主 Agent 访问下游时应使用 V1.3.2 建立的身份，下游日志中记录的主体为该 Agent</t>
+    <t>Downstream systems</t>
+  </si>
+  <si>
+    <t>When an autonomous agent accesses downstream systems, it shall use the identity established under V1.3.2, and the principal recorded in downstream logs shall be that agent</t>
   </si>
   <si>
     <t>V1.3.4</t>
   </si>
   <si>
-    <t>自主 Agent 访问下游应使用短时效令牌，不使用长期静态密钥</t>
+    <t>When an autonomous agent accesses downstream systems, it shall use short-lived tokens and shall not use long-term static keys</t>
   </si>
   <si>
     <t>V1.3.5</t>
   </si>
   <si>
-    <t>自主 Agent 的密钥和证书应有签发、轮换和吊销流程，轮换周期设上限</t>
+    <t>The keys and certificates of an autonomous agent shall have processes for issuance, rotation, and revocation, and the rotation period shall have an upper limit</t>
   </si>
   <si>
     <t>V1.4.1</t>
   </si>
   <si>
-    <t>V1.4 工作负载身份</t>
-  </si>
-  <si>
-    <t>平台应为每个会话的执行实例签发短期工作负载身份，并与该实例绑定</t>
-  </si>
-  <si>
-    <t>为会话分配独立执行实例（如容器、沙箱或虚拟机）的平台</t>
+    <t>V1.4 Workload Identity</t>
+  </si>
+  <si>
+    <t>The platform shall issue a short-lived workload identity to the execution instance of each session and bind it to that instance</t>
+  </si>
+  <si>
+    <t>Platforms that assign an independent execution instance (such as a container, sandbox, or virtual machine) to each session</t>
   </si>
   <si>
     <t>V1.4.2</t>
@@ -209,1672 +209,1672 @@
     <t>Harness</t>
   </si>
   <si>
-    <t>工作负载身份的凭证应对模型不可见，不进入上下文和工具返回</t>
+    <t>The credentials of the workload identity shall be invisible to the model and shall not enter the context or tool return values</t>
   </si>
   <si>
     <t>V1.4.3</t>
   </si>
   <si>
-    <t>出口网关</t>
-  </si>
-  <si>
-    <t>出口网关应只依据工作负载身份确定用户和 Agent，忽略请求中自报的用户或 Agent 标识</t>
+    <t>Egress gateway</t>
+  </si>
+  <si>
+    <t>The egress gateway shall determine the user and agent solely from the workload identity and shall ignore user or agent identifiers self-reported in the request</t>
   </si>
   <si>
     <t>V1.4.4</t>
   </si>
   <si>
-    <t>会话结束或执行实例销毁时，应立即吊销对应的工作负载身份</t>
+    <t>When a session ends or an execution instance is destroyed, the corresponding workload identity shall be revoked immediately</t>
   </si>
   <si>
     <t>V1.4.5</t>
   </si>
   <si>
-    <t>平台签发工作负载身份前应对执行实例做工作负载证明（如 SPIFFE/SPIRE 的节点证明和工作负载证明），证明失败不签发</t>
+    <t>Before issuing a workload identity, the platform shall perform workload attestation on the execution instance (such as node attestation and workload attestation in SPIFFE/SPIRE). The identity shall not be issued if attestation fails.</t>
   </si>
   <si>
     <t>V1.5.1</t>
   </si>
   <si>
-    <t>V1.5 外部主体</t>
-  </si>
-  <si>
-    <t>应通过身份联邦接入外部主体，不为其创建共享账号</t>
-  </si>
-  <si>
-    <t>向客户或合作伙伴开放 Agent 能力的平台</t>
+    <t>V1.5 External Principals</t>
+  </si>
+  <si>
+    <t>External principals shall be accessed through identity federation, and no shared account shall be created for them</t>
+  </si>
+  <si>
+    <t>Platforms that open agent capabilities to customers or partners</t>
   </si>
   <si>
     <t>V1.5.2</t>
   </si>
   <si>
-    <t>策略决策点</t>
-  </si>
-  <si>
-    <t>外部主体应只能访问为其开放的工作空间和接口</t>
+    <t>Policy decision point</t>
+  </si>
+  <si>
+    <t>External principals shall have access only to the workspaces and interfaces made available to them</t>
   </si>
   <si>
     <t>V1.5.3</t>
   </si>
   <si>
-    <t>审计</t>
-  </si>
-  <si>
-    <t>外部主体的调用应单独记录审计，可按外部组织筛选</t>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>Invocations by external principals shall be recorded separately in the audit log and shall be filterable by external organization</t>
   </si>
   <si>
     <t>V2.1.1</t>
   </si>
   <si>
-    <t>V2 委托与有效权限</t>
-  </si>
-  <si>
-    <t>V2.1 代表用户访问</t>
-  </si>
-  <si>
-    <t>用户在场时，Agent 访问下游应携带发起用户的身份，由下游按该用户作出授权判定；下游不支持用户级授权判定的按 V4.4 执行</t>
+    <t>V2 Delegation and Effective Permissions</t>
+  </si>
+  <si>
+    <t>V2.1 Access on Behalf of a User</t>
+  </si>
+  <si>
+    <t>When the user is present, an agent accessing downstream systems shall carry the identity of the initiating user, and the downstream system shall make its authorization decision based on that user. Downstream systems that do not support user-level authorization decisions are handled under V4.4.</t>
   </si>
   <si>
     <t>V2.1.2</t>
   </si>
   <si>
-    <t>不应使用权限高于发起用户的共享凭证替用户访问下游，只支持共享静态凭证的下游按 V4.4 执行补偿控制</t>
+    <t>Shared credentials with higher permissions than the initiating user shall not be used to access downstream systems on the user's behalf. Downstream systems that support only shared static credentials are handled by compensating controls under V4.4.</t>
   </si>
   <si>
     <t>V2.1.3</t>
   </si>
   <si>
-    <t>下游令牌应同时标识发起用户和执行的 Agent（如 RFC 8693 的 act 声明）</t>
+    <t>Downstream tokens shall identify both the initiating user and the executing agent (such as the act claim in RFC 8693)</t>
   </si>
   <si>
     <t>V2.2.1</t>
   </si>
   <si>
-    <t>V2.2 有效权限</t>
-  </si>
-  <si>
-    <t>每次调用的有效权限应取用户权限与 Agent 授权范围的交集</t>
+    <t>V2.2 Effective Permissions</t>
+  </si>
+  <si>
+    <t>The effective permissions of each invocation shall be the intersection of the user's permissions and the agent authorization scope</t>
   </si>
   <si>
     <t>V2.2.2</t>
   </si>
   <si>
-    <t>有效权限应由策略决策点计算，不依赖系统提示词或模型的判断</t>
+    <t>Effective permissions shall be computed by the policy decision point and shall not depend on the system prompt or on the model's judgment</t>
   </si>
   <si>
     <t>V2.2.3</t>
   </si>
   <si>
-    <t>任务开始时应声明所需的工具和数据范围，运行中只授予声明范围内的权限；声明由用户或 Agent 配置给出，模型提出的范围须经用户确认后生效</t>
+    <t>At the start of a task, the required tool and data scope shall be declared. During execution, only permissions within the declared scope shall be granted. The declaration is provided by the user or by agent configuration, and any scope proposed by the model shall take effect only after user confirmation.</t>
   </si>
   <si>
     <t>V2.2.4</t>
   </si>
   <si>
-    <t>超出任务声明范围的调用应被拒绝或转为审批</t>
+    <t>Invocations beyond the task's declared scope shall be rejected or require approval</t>
   </si>
   <si>
     <t>V2.2.5</t>
   </si>
   <si>
-    <t>有效权限应在每次工具调用时重新计算，不沿用会话开始时的授权结果</t>
+    <t>Effective permissions shall be recomputed on each tool invocation and shall not reuse the authorization result from the start of the session</t>
   </si>
   <si>
     <t>V2.2.6</t>
   </si>
   <si>
-    <t>高风险操作的授权应细化到具体资源和参数（如用 RFC 9396 RAR 描述授权细节），不只授予粗粒度角色</t>
+    <t>Authorization for high-risk operations shall be refined to specific resources and parameters (for example, using RFC 9396 Rich Authorization Requests to describe the authorization details) and shall not grant only coarse-grained roles</t>
   </si>
   <si>
     <t>V2.3.1</t>
   </si>
   <si>
-    <t>V2.3 离线委托任务</t>
-  </si>
-  <si>
-    <t>离线委托任务应以创建用户为根，创建时固定权限上限，之后只能收窄</t>
-  </si>
-  <si>
-    <t>支持定时任务或长时任务的平台</t>
+    <t>V2.3 Offline Delegated Tasks</t>
+  </si>
+  <si>
+    <t>An offline delegated task shall be rooted in its creating user. The permission upper limit shall be fixed at creation and can only be narrowed thereafter.</t>
+  </si>
+  <si>
+    <t>Platforms that support scheduled or long-running tasks</t>
   </si>
   <si>
     <t>V2.3.2</t>
   </si>
   <si>
-    <t>每次运行前应复查创建用户的账号状态和当前权限</t>
+    <t>The account status and current permissions of the creating user shall be rechecked before each run</t>
   </si>
   <si>
     <t>V2.3.3</t>
   </si>
   <si>
-    <t>调度器应只保存任务标识，不保存用户凭证或可直接使用的令牌</t>
+    <t>The scheduler shall store only task identifiers and shall not store user credentials or directly usable tokens</t>
   </si>
   <si>
     <t>V2.3.4</t>
   </si>
   <si>
-    <t>管理面</t>
-  </si>
-  <si>
-    <t>创建用户被禁用后，其离线委托任务应自动停止并通知该 Agent 的负责人</t>
+    <t>Management plane</t>
+  </si>
+  <si>
+    <t>When the creating user is disabled, their offline delegated tasks shall stop automatically, and the owner of the agent shall be notified</t>
   </si>
   <si>
     <t>V2.3.5</t>
   </si>
   <si>
-    <t>创建用户离职或转岗后仍需继续运行的任务，应在其账号禁用前转为自主 Agent，并重新审批授权</t>
+    <t>For tasks that must continue running after the creating user leaves or changes roles, the tasks shall be converted to autonomous agents and reauthorized through approval before the user's account is disabled</t>
   </si>
   <si>
     <t>V2.3.6</t>
   </si>
   <si>
-    <t>离线委托任务的授权应设到期时间，到期后需创建用户重新确认</t>
+    <t>The authorization for an offline delegated task shall have an expiration time, after which the creating user must reconfirm it</t>
   </si>
   <si>
     <t>V2.4.1</t>
   </si>
   <si>
-    <t>V2.4 Agent 间委托</t>
-  </si>
-  <si>
-    <t>下游 Agent 的有效权限不应超过发起用户的权限与上游的委托范围，发起用户不能经由下游 Agent 获得其本人没有的权限</t>
-  </si>
-  <si>
-    <t>支持多 Agent 协作或子 Agent 的平台</t>
+    <t>V2.4 Inter-Agent Delegation</t>
+  </si>
+  <si>
+    <t>The effective permissions of a downstream agent shall not exceed the permissions of the initiating user or the delegation scope granted by the upstream agent. The initiating user shall not obtain, through a downstream agent, permissions that the user does not hold.</t>
+  </si>
+  <si>
+    <t>Platforms that support multi-agent collaboration or sub-agents</t>
   </si>
   <si>
     <t>V2.4.2</t>
   </si>
   <si>
-    <t>Harness 派生的子 Agent，可用工具和权限应是父 Agent 的子集</t>
+    <t>For sub-agents derived by the harness, the available tools and permissions shall be a subset of those of the parent agent</t>
   </si>
   <si>
     <t>V2.4.3</t>
   </si>
   <si>
-    <t>委托链应由平台构建和记录，不采信未经平台或可信授权服务器签名的身份声明</t>
+    <t>The delegation chain shall be constructed and recorded by the platform. Identity assertions not signed by the platform or by a trusted authorization server shall not be accepted.</t>
   </si>
   <si>
     <t>V2.4.4</t>
   </si>
   <si>
-    <t>应显式配置哪些 Agent 可以调用哪些 Agent，未配置的调用被拒绝</t>
+    <t>Which agents may invoke which other agents shall be explicitly configured. Invocations that are not configured shall be rejected.</t>
   </si>
   <si>
     <t>V2.4.5</t>
   </si>
   <si>
-    <t>应限制委托链深度，并检测和阻断循环调用</t>
+    <t>The depth of the delegation chain shall be limited, and circular invocations shall be detected and blocked</t>
   </si>
   <si>
     <t>V2.4.6</t>
   </si>
   <si>
-    <t>多跳委托时，下游令牌应携带完整的执行者链（如 RFC 8693 中嵌套的 act 声明），使下游能据此授权</t>
+    <t>In multi-hop delegation, downstream tokens shall carry the complete executor chain (such as nested act claims in RFC 8693) so that downstream systems can make authorization decisions accordingly</t>
   </si>
   <si>
     <t>V2.4.7</t>
   </si>
   <si>
-    <t>在同一信任域内跨服务调用时，应沿调用链传递携带用户、Agent 和任务上下文的令牌（如 Transaction Token 草案），下游据此授权</t>
+    <t>For cross-service invocations within the same trust domain, tokens carrying user, agent, and task context shall be propagated along the call chain (such as the Transaction Tokens draft), so that downstream systems can make authorization decisions accordingly</t>
   </si>
   <si>
     <t>V2.5.1</t>
   </si>
   <si>
-    <t>V2.5 用户间委托与临时提权</t>
-  </si>
-  <si>
-    <t>用户允许他人代为使用自己的 Agent 时（如助理代主管），应显式登记委托关系，并限定范围和期限</t>
-  </si>
-  <si>
-    <t>支持用户代他人使用 Agent，或支持 Agent 临时提权的平台</t>
+    <t>V2.5 Inter-User Delegation and Temporary Privilege Elevation</t>
+  </si>
+  <si>
+    <t>When a user permits others to operate the user's agent on their behalf (for example, an assistant acting for a manager), the delegation relationship shall be explicitly registered, with a defined scope and period</t>
+  </si>
+  <si>
+    <t>Platforms that let users operate agents on behalf of others, or that support temporary privilege elevation for agents</t>
   </si>
   <si>
     <t>V2.5.2</t>
   </si>
   <si>
-    <t>代为操作时，审计应同时记录委托人和实际操作人</t>
+    <t>When operating on behalf of another person, audit shall record both the principal and the person who actually performed the operation</t>
   </si>
   <si>
     <t>V2.5.3</t>
   </si>
   <si>
-    <t>Agent 需要超出其授权范围的权限时，应经申请和审批限时授予，到期自动收回</t>
+    <t>When an agent requires permissions beyond its authorization scope, they shall be granted for a limited time through request and approval, and they shall be withdrawn automatically upon expiry</t>
   </si>
   <si>
     <t>V2.6.1</t>
   </si>
   <si>
-    <t>V2.6 事件触发授权</t>
-  </si>
-  <si>
-    <t>入站事件应校验签名和来源，未通过校验的事件被拒绝</t>
-  </si>
-  <si>
-    <t>支持 Webhook、告警、工单等事件触发 Agent 的平台</t>
+    <t>V2.6 Event-Triggered Authorization</t>
+  </si>
+  <si>
+    <t>Inbound events shall have their signatures and sources verified, and events that fail verification shall be rejected</t>
+  </si>
+  <si>
+    <t>Platforms that support agents triggered by events such as webhooks, alerts, or tickets</t>
   </si>
   <si>
     <t>V2.6.2</t>
   </si>
   <si>
-    <t>每条触发规则应绑定执行身份，即自主 Agent 的身份或规则配置人的身份</t>
+    <t>Each trigger rule shall be bound to an execution identity, namely the identity of an autonomous agent or the identity of the person who configured the rule</t>
   </si>
   <si>
     <t>V2.6.3</t>
   </si>
   <si>
-    <t>触发规则的创建和修改应记录审计，并标明配置人</t>
+    <t>The creation and modification of trigger rules shall be recorded in the audit log and shall identify the person who configured them</t>
   </si>
   <si>
     <t>V3.1.1</t>
   </si>
   <si>
-    <t>V3 授权决策</t>
-  </si>
-  <si>
-    <t>V3.1 操作风险分级</t>
-  </si>
-  <si>
-    <t>应为每个工具标注操作类别（至少区分读取、写入、删除、外发、资金操作和生产变更）和风险等级</t>
+    <t>V3 Authorization Decisions</t>
+  </si>
+  <si>
+    <t>V3.1 Operation Risk Classification</t>
+  </si>
+  <si>
+    <t>Each tool shall be labeled with an operation category (distinguishing at least read, write, delete, outbound transfer, fund operation, and production change) and a risk level</t>
   </si>
   <si>
     <t>V3.1.2</t>
   </si>
   <si>
-    <t>风险等级应由平台按工具和参数判定，不采用模型给出的风险评估</t>
+    <t>The risk level shall be determined by the platform based on the tool and its parameters, and shall not be based on the risk assessment given by the model</t>
   </si>
   <si>
     <t>V3.1.3</t>
   </si>
   <si>
-    <t>每个风险等级应对应确定的处置方式，如自动执行、事后通知、事前审批、二次认证或拒绝</t>
+    <t>Each risk level shall correspond to a defined disposition, such as automatic execution, after-the-fact notification, prior approval, step-up authentication, or rejection</t>
   </si>
   <si>
     <t>V3.1.4</t>
   </si>
   <si>
-    <t>同一工具在影响范围不同的参数下（如删除 1 条与批量删除）应能落入不同等级</t>
+    <t>The same tool, under parameters with different scopes of impact (such as deleting one record versus bulk deletion), shall be able to fall into different levels</t>
   </si>
   <si>
     <t>V3.2.1</t>
   </si>
   <si>
-    <t>V3.2 工具调用前置校验</t>
-  </si>
-  <si>
-    <t>每次工具调用执行前都应经过策略检查，检查在 Agent 无法修改的组件中执行（平台托管的 Harness、策略决策点或出口网关）；授权决定不采用被检查 Agent 所用模型的输出</t>
+    <t>V3.2 Pre-Invocation Validation for Tool Calls</t>
+  </si>
+  <si>
+    <t>Every tool invocation shall pass a policy check before execution. The check shall run in a component that the agent cannot modify (a platform-hosted harness, the policy decision point, or the egress gateway). Authorization decisions shall not be based on the output of the model used by the agent being checked.</t>
   </si>
   <si>
     <t>V3.2.2</t>
   </si>
   <si>
-    <t>安全约束应由策略执行点（Harness 或出口网关）按策略决策点的决定强制执行，不能只写在系统提示词里</t>
+    <t>Security constraints shall be enforced by the policy enforcement point (the harness or the egress gateway) according to the decisions of the policy decision point, and they shall not exist only in the system prompt</t>
   </si>
   <si>
     <t>V3.2.3</t>
   </si>
   <si>
-    <t>前置检查的策略和钩子应由平台下发，Agent 自身不能修改或绕过</t>
+    <t>The policies and hooks for pre-execution checks shall be distributed by the platform, and the agent itself shall not be able to modify or bypass them</t>
   </si>
   <si>
     <t>V3.2.4</t>
   </si>
   <si>
-    <t>策略检查出错或超时时应默认拒绝</t>
+    <t>When a policy check errors or times out, the default shall be to deny</t>
   </si>
   <si>
     <t>V3.2.5</t>
   </si>
   <si>
-    <t>策略决策点应通过标准化授权接口（如 OpenID AuthZEN）与策略执行点交互，便于替换策略引擎</t>
+    <t>The policy decision point shall interact with the policy enforcement point through a standardized authorization interface (such as OpenID AuthZEN) to facilitate replacement of the policy engine</t>
   </si>
   <si>
     <t>V3.3.1</t>
   </si>
   <si>
-    <t>V3.3 工具暴露面</t>
-  </si>
-  <si>
-    <t>交给模型的工具清单应按当前有效权限过滤，模型看不到无权使用的工具</t>
+    <t>V3.3 Tool Exposure</t>
+  </si>
+  <si>
+    <t>The tool list provided to the model shall be filtered by current effective permissions, so that the model cannot see tools it is not authorized to use</t>
   </si>
   <si>
     <t>V3.3.2</t>
   </si>
   <si>
-    <t>工具清单裁剪之外，执行前仍应按 V3.2 校验</t>
+    <t>Beyond trimming the tool list, V3.2 validation shall still be applied before execution</t>
   </si>
   <si>
     <t>V3.4.1</t>
   </si>
   <si>
-    <t>V3.4 人工审批</t>
-  </si>
-  <si>
-    <t>高风险操作应在执行前取得有权批准该操作的人批准；未列入双人控制的操作可由发起用户本人批准</t>
+    <t>V3.4 Human Approval</t>
+  </si>
+  <si>
+    <t>High-risk operations shall be approved, before execution, by a person authorized to approve them. Operations not subject to dual control may be approved by the initiating user.</t>
   </si>
   <si>
     <t>V3.4.2</t>
   </si>
   <si>
-    <t>审批内容应由平台根据真实调用参数生成，不使用模型撰写的摘要</t>
+    <t>Approval content shall be generated by the platform from the actual invocation parameters and shall not use a summary written by the model</t>
   </si>
   <si>
     <t>V3.4.3</t>
   </si>
   <si>
-    <t>执行时应校验实际参数与审批时一致，不一致则拒绝；按 V3.4.6 事先批准的计划执行的调用，校验其在计划范围内</t>
+    <t>At execution, the actual parameters shall be verified to match those at approval, and execution shall be rejected if they do not match. For invocations executed under a pre-approved plan per V3.4.6, the invocation shall be verified to be within the plan's scope.</t>
   </si>
   <si>
     <t>V3.4.4</t>
   </si>
   <si>
-    <t>审批应设有效期，过期未批视为拒绝</t>
+    <t>Approvals shall have a validity period, and an approval request that expires without a decision shall be treated as rejected</t>
   </si>
   <si>
     <t>V3.4.5</t>
   </si>
   <si>
-    <t>应限制审批请求的频率并合并同类请求，防止审批疲劳</t>
+    <t>The frequency of approval requests shall be limited and similar requests shall be merged to prevent approval fatigue</t>
   </si>
   <si>
     <t>V3.4.6</t>
   </si>
   <si>
-    <t>应支持事先批准的执行计划，写明工具、资源范围和上限；计划范围内的操作不再逐次审批，超出范围即中止并重新审批</t>
+    <t>The platform shall support pre-approved execution plans that specify tools, resource scope, and limits. Operations within the plan's scope are not approved individually each time. Operations exceeding the scope shall be aborted and reapproved.</t>
   </si>
   <si>
     <t>V3.5.1</t>
   </si>
   <si>
-    <t>V3.5 二次认证与持续访问评估</t>
-  </si>
-  <si>
-    <t>资金、生产变更、批量删除等操作应要求用户完成二次认证（如重新完成 MFA）</t>
+    <t>V3.5 Step-Up Authentication and Continuous Access Evaluation</t>
+  </si>
+  <si>
+    <t>Operations such as fund transfers, production changes, and bulk deletion shall require the user to complete step-up authentication (such as re-completing MFA)</t>
   </si>
   <si>
     <t>V3.5.2</t>
   </si>
   <si>
-    <t>平台应接收 IdP 的会话风险信号（如 CAEP），风险升高时降低 Agent 可执行的操作等级或暂停 Agent</t>
+    <t>The platform shall receive session risk signals from the IdP (such as CAEP). When risk rises, it shall lower the level of operations the agent may perform or suspend the agent.</t>
   </si>
   <si>
     <t>V3.6.1</t>
   </si>
   <si>
-    <t>V3.6 职责分离</t>
-  </si>
-  <si>
-    <t>互斥职责（如提交与审批、开发与上线）不应分配给同一个 Agent</t>
+    <t>V3.6 Separation of Duties</t>
+  </si>
+  <si>
+    <t>Mutually exclusive duties (such as submission and approval, or development and release) shall not be assigned to the same agent</t>
   </si>
   <si>
     <t>V3.6.2</t>
   </si>
   <si>
-    <t>对按职责分离要求双人控制的操作（如付款、生产变更、权限授予），审批人不应是发起人本人，也不应是代发起人行事的 Agent</t>
+    <t>For operations that require dual control under separation of duties (such as payments, production changes, and permission grants), the approver shall not be the initiator, nor an agent acting on the initiator's behalf</t>
   </si>
   <si>
     <t>V3.7.1</t>
   </si>
   <si>
-    <t>V3.7 持久化操作</t>
-  </si>
-  <si>
-    <t>Agent 创建或修改定时任务、触发规则、Webhook、转发规则和 Skill，应经用户审批后才生效</t>
+    <t>V3.7 Persistent Operations</t>
+  </si>
+  <si>
+    <t>When an agent creates or modifies scheduled tasks, trigger rules, webhooks, forwarding rules, or skills, such changes shall take effect only after user approval</t>
   </si>
   <si>
     <t>V3.7.2</t>
   </si>
   <si>
-    <t>由 Agent 创建的全部持久化对象应能在管理面集中列出，并标明创建来源</t>
+    <t>The management plane shall be able to centrally list all persistent objects created by an agent and indicate the source of their creation</t>
   </si>
   <si>
     <t>V3.8.1</t>
   </si>
   <si>
-    <t>V3.8 数量、速率与配额</t>
-  </si>
-  <si>
-    <t>应按用户、Agent 和操作类型设置速率、批量和导出上限</t>
+    <t>V3.8 Quantity, Rate, and Quota</t>
+  </si>
+  <si>
+    <t>Rate, bulk, and export limits shall be set by user, agent, and operation type</t>
   </si>
   <si>
     <t>V3.8.2</t>
   </si>
   <si>
-    <t>超出上限的请求应被拦截并告警</t>
+    <t>Requests exceeding limits shall be blocked and alerted</t>
   </si>
   <si>
     <t>V3.8.3</t>
   </si>
   <si>
-    <t>应按部门、用户或 Agent 设置模型调用预算，超额时暂停或转为审批</t>
+    <t>Model invocation budgets shall be set by department, user, or agent. When a budget is exceeded, the invocations shall be paused or require approval.</t>
   </si>
   <si>
     <t>V3.8.4</t>
   </si>
   <si>
-    <t>每次 Agent 运行应设置最大工具调用次数、最长运行时长和最大模型调用开销，由平台强制执行，达到上限即中止并通知发起人或负责人</t>
+    <t>Each agent run shall have a maximum number of tool invocations, a maximum run duration, and a maximum model invocation cost, enforced by the platform. When a limit is reached, the run shall be aborted and the initiator or owner notified.</t>
   </si>
   <si>
     <t>V4.1.1</t>
   </si>
   <si>
-    <t>V4 凭证与出口执行</t>
-  </si>
-  <si>
-    <t>V4.1 凭证托管与注入</t>
-  </si>
-  <si>
-    <t>访问下游所需的令牌和密钥应由平台托管，平台托管的执行环境、上下文和模型中只出现占位凭证，V5.2.2 规定的情形除外</t>
+    <t>V4 Credentials and Egress Enforcement</t>
+  </si>
+  <si>
+    <t>V4.1 Credential Custody and Injection</t>
+  </si>
+  <si>
+    <t>Tokens and keys required to access downstream systems shall be held by the platform. Only placeholder credentials shall appear in platform-hosted execution environments, in the context, and in the model, except for the cases specified in V5.2.2.</t>
   </si>
   <si>
     <t>V4.1.2</t>
   </si>
   <si>
-    <t>每个托管凭证应绑定允许的目标域名和路径，网关只在目标匹配时注入真实凭证</t>
+    <t>Each managed credential shall be bound to permitted target domain names and paths, and the gateway shall inject the real credential only when the target matches</t>
   </si>
   <si>
     <t>V4.1.3</t>
   </si>
   <si>
-    <t>网关不应把凭证注入 URL 或查询参数；非 HTTP 协议的认证应由网关或平台侧代理完成，凭证不进入执行环境</t>
+    <t>The gateway shall not inject credentials into URLs or query parameters. Authentication for non-HTTP protocols shall be completed by the gateway or a platform-side proxy, and credentials shall not enter the execution environment.</t>
   </si>
   <si>
     <t>V4.1.4</t>
   </si>
   <si>
-    <t>目标不匹配的替换请求应被拒绝并告警</t>
+    <t>Substitution requests whose target does not match shall be rejected and alerted</t>
   </si>
   <si>
     <t>V4.1.5</t>
   </si>
   <si>
-    <t>下游响应中回显的凭证应在返回执行环境前被剔除</t>
+    <t>Credentials echoed in downstream responses shall be stripped before the response is returned to the execution environment</t>
   </si>
   <si>
     <t>V4.1.6</t>
   </si>
   <si>
-    <t>平台应提供托管授权流程（如 OAuth），用户无需把个人凭证或 API Key 直接交给 Agent</t>
+    <t>The platform shall provide a managed authorization flow (such as OAuth), so that users do not need to hand personal credentials or API keys directly to the agent</t>
   </si>
   <si>
     <t>V4.1.7</t>
   </si>
   <si>
-    <t>对话和上传文件中出现的凭证应被识别，并阻止其写入记忆、产出物或 Agent 配置</t>
+    <t>Credentials appearing in conversations and uploaded files shall be identified, and their writing into memory, output artifacts, or agent configuration shall be blocked</t>
   </si>
   <si>
     <t>V4.2.1</t>
   </si>
   <si>
-    <t>V4.2 统一出口</t>
-  </si>
-  <si>
-    <t>Agent 对执行环境之外的全部访问应只经过出口网关</t>
+    <t>V4.2 Unified Egress</t>
+  </si>
+  <si>
+    <t>All of an agent's access outside the execution environment shall pass only through the egress gateway</t>
   </si>
   <si>
     <t>V4.2.2</t>
   </si>
   <si>
-    <t>执行环境</t>
-  </si>
-  <si>
-    <t>执行环境的网络应默认拒绝出站，只放行出口网关</t>
+    <t>Execution environment</t>
+  </si>
+  <si>
+    <t>Network egress from the execution environment shall be denied by default, and only traffic to the egress gateway shall be allowed</t>
   </si>
   <si>
     <t>V4.2.3</t>
   </si>
   <si>
-    <t>内网服务和数据库应拒绝来自执行环境网段、绕过网关的直连</t>
+    <t>Internal network services and databases shall reject direct connections from the execution environment's network segment that bypass the gateway</t>
   </si>
   <si>
     <t>V4.2.4</t>
   </si>
   <si>
-    <t>应定期扫描执行环境、Agent 配置和镜像中的硬编码凭证</t>
+    <t>Hard-coded credentials in the execution environment, agent configurations, and images shall be scanned periodically</t>
   </si>
   <si>
     <t>V4.2.5</t>
   </si>
   <si>
-    <t>平台应维护已登记的下游系统清单（地址、所属系统和数据级别），出口网关据此区分企业内访问与外发</t>
+    <t>The platform shall maintain an inventory of registered downstream systems (addresses, owning systems, and data classification), against which the egress gateway distinguishes intra-enterprise access from outbound transfer</t>
   </si>
   <si>
     <t>V4.3.1</t>
   </si>
   <si>
-    <t>V4.3 下游身份传递</t>
-  </si>
-  <si>
-    <t>访问第三方 SaaS 时，应取得用户级授权（由用户本人完成 OAuth 授权，或经企业 IdP 换取用户级令牌），不使用跨用户共享的应用凭证</t>
+    <t>V4.3 Downstream Identity Propagation</t>
+  </si>
+  <si>
+    <t>When accessing third-party SaaS, user-level authorization shall be obtained, either by the user completing OAuth authorization personally or by obtaining a user-level token from the enterprise IdP via token exchange. Application credentials shared across users shall not be used.</t>
   </si>
   <si>
     <t>V4.3.2</t>
   </si>
   <si>
-    <t>用户撤销授权后，平台应立即停止使用对应凭证</t>
+    <t>When a user revokes authorization, the platform shall immediately stop using the corresponding credential</t>
   </si>
   <si>
     <t>V4.3.3</t>
   </si>
   <si>
-    <t>下游支持令牌交换时，应通过企业 IdP 按 RFC 8693，或按基于 RFC 8693 与 RFC 7523 的 ID-JAG，换取用户级短期令牌</t>
+    <t>When a downstream system supports token exchange, a user-level short-lived token shall be obtained through the enterprise IdP per RFC 8693, or through ID-JAG based on RFC 8693 and RFC 7523</t>
   </si>
   <si>
     <t>V4.4.1</t>
   </si>
   <si>
-    <t>V4.4 静态凭证遗留系统</t>
-  </si>
-  <si>
-    <t>遗留系统的共享密钥应由平台托管，不下发到执行环境</t>
-  </si>
-  <si>
-    <t>存在只支持共享静态凭证的下游系统的平台</t>
+    <t>V4.4 Legacy Systems with Static Credentials</t>
+  </si>
+  <si>
+    <t>Shared secrets of legacy systems shall be held by the platform and shall not be distributed to the execution environment</t>
+  </si>
+  <si>
+    <t>Platforms with downstream systems that support only shared static credentials</t>
   </si>
   <si>
     <t>V4.4.2</t>
   </si>
   <si>
-    <t>网关应按用户在接口级和操作级作出授权判定，弥补下游缺失的用户级授权</t>
+    <t>The gateway shall make user-level authorization decisions at the interface and operation levels to compensate for the lack of user-level authorization in the downstream system</t>
   </si>
   <si>
     <t>V4.4.3</t>
   </si>
   <si>
-    <t>网关应向下游附带签名的用户身份信息，供下游校验和逐步改造</t>
+    <t>The gateway shall attach a signed user identity to downstream requests so that downstream systems can verify it and progressively adopt user-level authorization</t>
   </si>
   <si>
     <t>V4.4.4</t>
   </si>
   <si>
-    <t>应登记由网关代为作出用户级授权判定的下游系统，并纳入定期复核</t>
+    <t>Downstream systems for which the gateway makes user-level authorization decisions on their behalf shall be registered and included in periodic review</t>
   </si>
   <si>
     <t>V4.5.1</t>
   </si>
   <si>
-    <t>V4.5 MCP 调用</t>
-  </si>
-  <si>
-    <t>远程 MCP Server 的请求应经过出口网关，并携带用户身份</t>
-  </si>
-  <si>
-    <t>支持 MCP 的平台</t>
+    <t>V4.5 MCP Invocation</t>
+  </si>
+  <si>
+    <t>Requests to remote MCP servers shall pass through the egress gateway and carry the user identity</t>
+  </si>
+  <si>
+    <t>Platforms that support MCP</t>
   </si>
   <si>
     <t>V4.5.2</t>
   </si>
   <si>
-    <t>平台自建或托管的 MCP Server 不应持有供所有用户共用的长期凭证</t>
+    <t>MCP servers built or hosted by the platform shall not hold long-term credentials shared by all users</t>
   </si>
   <si>
     <t>V4.5.3</t>
   </si>
   <si>
-    <t>本地运行的 MCP 进程应同样只获得占位凭证，出网受执行环境的网络策略约束</t>
+    <t>Locally running MCP processes shall likewise obtain only placeholder credentials, and their outbound network access shall be constrained by the execution environment's network policy</t>
   </si>
   <si>
     <t>V4.5.4</t>
   </si>
   <si>
-    <t>支持 Enterprise-Managed Authorization 扩展的 MCP Server，应通过企业 IdP 授权接入</t>
+    <t>MCP servers that support the Enterprise-Managed Authorization extension shall be connected with authorization through the enterprise IdP</t>
   </si>
   <si>
     <t>V4.5.5</t>
   </si>
   <si>
-    <t>平台自建或托管的 MCP Server 应只接受签发给自身的令牌（校验签发方和受众，如使用 RFC 8707 资源指示符），不应把收到的令牌透传给下游 API</t>
+    <t>MCP servers built or hosted by the platform shall accept only tokens issued for them (audience-restricted to the server), verifying the issuer and audience (for example using the RFC 8707 resource indicator), and shall not pass received tokens through to downstream APIs</t>
   </si>
   <si>
     <t>V4.5.6</t>
   </si>
   <si>
-    <t>平台应保存已审核 MCP Server 的工具定义快照，工具名称、描述或参数结构变化后，在重新审核前不向模型暴露</t>
+    <t>The platform shall retain a snapshot of the tool definitions of reviewed MCP servers. After any change in tool name, description, or parameter structure, the changed tools shall not be exposed to the model until they are reviewed again.</t>
   </si>
   <si>
     <t>V4.6.1</t>
   </si>
   <si>
-    <t>V4.6 令牌生命周期</t>
-  </si>
-  <si>
-    <t>网关注入或换取的下游令牌应设置短有效期</t>
+    <t>V4.6 Token Lifecycle</t>
+  </si>
+  <si>
+    <t>Downstream tokens injected or exchanged by the gateway shall have a short validity period</t>
   </si>
   <si>
     <t>V4.6.2</t>
   </si>
   <si>
-    <t>对支持的下游，令牌应采用发送方绑定（DPoP 或 mTLS），防止被盗后重放</t>
+    <t>For supported downstream systems, tokens shall be sender-constrained (DPoP or mTLS) to prevent replay after theft</t>
   </si>
   <si>
     <t>V4.6.3</t>
   </si>
   <si>
-    <t>令牌应限定受众（audience），只能用于签发时指定的下游</t>
+    <t>Tokens shall be restricted to an audience and shall be usable only with the downstream system specified at issuance</t>
   </si>
   <si>
     <t>V4.7.1</t>
   </si>
   <si>
-    <t>V4.7 凭证库保护</t>
-  </si>
-  <si>
-    <t>托管凭证应加密存储，数据库和备份中不出现明文</t>
+    <t>V4.7 Credential Store Protection</t>
+  </si>
+  <si>
+    <t>Managed credentials shall be stored encrypted, and no plaintext shall appear in databases or backups</t>
   </si>
   <si>
     <t>V4.7.2</t>
   </si>
   <si>
-    <t>平台管理员和运维人员不应能读取或导出凭证明文</t>
+    <t>Platform administrators and operations personnel shall not be able to read or export plaintext credentials</t>
   </si>
   <si>
     <t>V4.7.3</t>
   </si>
   <si>
-    <t>只有出口网关能在调用时取用凭证，每次取用都应记录审计</t>
+    <t>Credentials shall be retrievable at invocation time only by the egress gateway, and each retrieval shall be recorded in the audit log</t>
   </si>
   <si>
     <t>V4.7.4</t>
   </si>
   <si>
-    <t>主密钥应由企业控制的 KMS 或 HSM 管理</t>
+    <t>The master key shall be managed by a KMS or HSM controlled by the enterprise</t>
   </si>
   <si>
     <t>V4.7.5</t>
   </si>
   <si>
-    <t>应支持按用户、按连接或全量批量轮换和吊销凭证</t>
+    <t>The platform shall support bulk rotation and revocation of credentials per user, per connection, or for all credentials</t>
   </si>
   <si>
     <t>V5.1.1</t>
   </si>
   <si>
-    <t>V5 执行隔离</t>
-  </si>
-  <si>
-    <t>V5.1 执行环境隔离</t>
-  </si>
-  <si>
-    <t>每个会话应使用独立的执行环境，不同用户之间、同一用户的不同会话之间不共享文件和进程</t>
-  </si>
-  <si>
-    <t>平台托管的执行环境；在员工终端上运行的 Agent 按 V5.4 执行</t>
+    <t>V5 Execution Isolation</t>
+  </si>
+  <si>
+    <t>V5.1 Execution Environment Isolation</t>
+  </si>
+  <si>
+    <t>Each session shall use an independent execution environment. Files and processes shall not be shared between different users, or between different sessions of the same user.</t>
+  </si>
+  <si>
+    <t>Platform-hosted execution environments; agents running on employee endpoints are handled under V5.4</t>
   </si>
   <si>
     <t>V5.1.2</t>
   </si>
   <si>
-    <t>执行环境应以非特权身份运行，不能访问宿主机或其他实例</t>
+    <t>The execution environment shall run under an unprivileged identity and shall not be able to access the host or other instances</t>
   </si>
   <si>
     <t>V5.1.3</t>
   </si>
   <si>
-    <t>会话结束后应销毁执行环境及其中的文件和临时凭证</t>
+    <t>After a session ends, the execution environment and its files and temporary credentials shall be destroyed</t>
   </si>
   <si>
     <t>V5.1.4</t>
   </si>
   <si>
-    <t>多个用户或租户共享宿主机的执行环境，应采用独立内核或用户态内核隔离，如 gVisor、Kata Containers 或 Firecracker 微虚拟机</t>
+    <t>Where multiple users or tenants share a host's execution environment, independent kernel or user-space kernel isolation shall be used, such as gVisor, Kata Containers, or Firecracker microVMs</t>
   </si>
   <si>
     <t>V5.2.1</t>
   </si>
   <si>
-    <t>V5.2 代码与命令执行</t>
-  </si>
-  <si>
-    <t>代码和命令应只在隔离的执行环境中运行，不在 Harness 或平台宿主上直接执行</t>
-  </si>
-  <si>
-    <t>支持代码或命令执行的平台</t>
+    <t>V5.2 Code and Command Execution</t>
+  </si>
+  <si>
+    <t>Code and commands shall run only in an isolated execution environment, and not directly on the harness or on the platform host</t>
+  </si>
+  <si>
+    <t>Platforms that support code or command execution</t>
   </si>
   <si>
     <t>V5.2.2</t>
   </si>
   <si>
-    <t>无法由出口网关注入的凭证（如需在客户端签名的云 API 凭证），应按用户和任务签发限定权限和目标资源的短期凭证（如 AWS STS），不放长期密钥</t>
+    <t>Credentials that cannot be injected by the egress gateway (such as cloud API credentials used for client-side request signing) shall be issued as short-lived credentials (such as AWS STS) scoped to specific permissions and target resources per user and task. Long-lived keys shall not be placed in the execution environment.</t>
   </si>
   <si>
     <t>V5.2.3</t>
   </si>
   <si>
-    <t>在员工终端或挂载持久数据的执行环境中，删除持久数据、提权和修改网络配置的命令应在执行前转为审批</t>
+    <t>On employee endpoints or in execution environments that mount persistent data, commands that delete persistent data, escalate privileges, or modify network configuration shall require approval before execution</t>
   </si>
   <si>
     <t>V5.2.4</t>
   </si>
   <si>
-    <t>依赖包应只能从企业认可的镜像源安装</t>
+    <t>Dependency packages shall be installed only from enterprise-approved mirror sources</t>
   </si>
   <si>
     <t>V5.3.1</t>
   </si>
   <si>
-    <t>V5.3 浏览器与桌面操作</t>
-  </si>
-  <si>
-    <t>平台提供浏览器环境时，Agent 应使用独立的浏览器配置，不复用用户已登录的个人会话</t>
-  </si>
-  <si>
-    <t>支持浏览器或桌面操作的平台</t>
+    <t>V5.3 Browser and Desktop Operations</t>
+  </si>
+  <si>
+    <t>When the platform provides a browser environment, the agent shall use an independent browser profile and shall not reuse the user's personal logged-in session</t>
+  </si>
+  <si>
+    <t>Platforms that support browser or desktop operations</t>
   </si>
   <si>
     <t>V5.3.2</t>
   </si>
   <si>
-    <t>提交会产生外部效果的表单（如下单、付款、发送消息、发布内容、修改账户设置）前应转为审批</t>
+    <t>Before a form that produces an external effect (such as placing an order, making a payment, sending a message, publishing content, or changing account settings) is submitted, the action shall require approval</t>
   </si>
   <si>
     <t>V5.3.3</t>
   </si>
   <si>
-    <t>应逐站点授权 Agent 可访问的网站，未授权站点被拦截</t>
+    <t>Websites that the agent may access shall be authorized site by site, and unauthorized sites shall be blocked</t>
   </si>
   <si>
     <t>V5.3.4</t>
   </si>
   <si>
-    <t>桌面操作应限定在用户授权的应用范围内</t>
+    <t>Desktop operations shall be limited to the scope of applications authorized by the user</t>
   </si>
   <si>
     <t>V5.3.5</t>
   </si>
   <si>
-    <t>在用户已登录的浏览器中运行的 Agent（如浏览器插件），应按站点白名单运行，默认拒绝未列入的站点，并默认禁止在身份认证、支付和管理后台类站点上操作</t>
+    <t>An agent running in a browser where the user is logged in (such as a browser extension) shall operate on a site allowlist, shall deny by default any site not on the list, and shall by default be prohibited from operating on identity authentication, payment, and administrative console sites</t>
   </si>
   <si>
     <t>V5.4.1</t>
   </si>
   <si>
-    <t>V5.4 端侧 Harness</t>
-  </si>
-  <si>
-    <t>端侧执行应默认放在系统级沙箱中，如 macOS Seatbelt 或 Linux bubblewrap</t>
-  </si>
-  <si>
-    <t>在员工终端上运行的 Agent，如编码 Agent、桌面助手</t>
+    <t>V5.4 Endpoint Harness</t>
+  </si>
+  <si>
+    <t>Endpoint execution shall by default be placed in a system-level sandbox, such as macOS Seatbelt or Linux bubblewrap</t>
+  </si>
+  <si>
+    <t>Agents running on employee endpoints, such as coding agents and desktop assistants</t>
   </si>
   <si>
     <t>V5.4.2</t>
   </si>
   <si>
-    <t>文件访问应按目录授权，默认不能读取密钥目录（如 ~/.ssh、~/.aws）和浏览器凭证存储</t>
+    <t>File access shall be authorized by directory. By default, reading directories containing keys or secrets (such as `~/.ssh` and `~/.aws`) and browser credential stores shall be denied.</t>
   </si>
   <si>
     <t>V5.4.3</t>
   </si>
   <si>
-    <t>在受管终端上，企业应能通过托管策略统一下发端侧策略，员工不能在本机关闭；未受管终端上的端侧 Agent 不应获得企业资源的访问凭证</t>
+    <t>On managed endpoints, the enterprise shall be able to distribute endpoint policies uniformly through managed policy, and employees shall not be able to disable them locally. Endpoint agents on unmanaged endpoints shall not obtain credentials for accessing enterprise resources.</t>
   </si>
   <si>
     <t>V5.4.4</t>
   </si>
   <si>
-    <t>端侧 Agent 访问企业资源应经过出口网关，不直接使用本机保存的企业凭证</t>
+    <t>Endpoint agents accessing enterprise resources shall pass through the egress gateway and shall not directly use enterprise credentials stored locally</t>
   </si>
   <si>
     <t>V5.5.1</t>
   </si>
   <si>
-    <t>V5.5 Harness 配置与权限模式</t>
-  </si>
-  <si>
-    <t>企业应能下发不可被本地配置覆盖的托管策略</t>
+    <t>V5.5 Harness Configuration and Permission Modes</t>
+  </si>
+  <si>
+    <t>The enterprise shall be able to distribute managed policies that cannot be overridden by local configuration</t>
   </si>
   <si>
     <t>V5.5.2</t>
   </si>
   <si>
-    <t>托管策略应能禁止或限制自动批准、跳过确认等模式</t>
+    <t>Managed policies shall be able to prohibit or restrict modes such as automatic approval and skipping confirmation</t>
   </si>
   <si>
     <t>V5.5.3</t>
   </si>
   <si>
-    <t>允许和禁止的工具清单应由企业统一配置</t>
+    <t>The lists of permitted and prohibited tools shall be configured centrally by the enterprise</t>
   </si>
   <si>
     <t>V5.5.4</t>
   </si>
   <si>
-    <t>项目目录（代码仓库或 IDE 中打开的工作区）中的规则文件、MCP 定义和钩子，应在用户确认信任后才加载</t>
+    <t>Rule files, MCP definitions, and hooks in the project directory (a code repository or a workspace opened in an IDE) shall be loaded only after the user confirms trust</t>
   </si>
   <si>
     <t>V5.5.5</t>
   </si>
   <si>
-    <t>项目目录中的上述配置变更后，应重新确认信任才能加载</t>
+    <t>After the above configuration in the project directory changes, trust shall be reconfirmed before it is loaded</t>
   </si>
   <si>
     <t>V5.5.6</t>
   </si>
   <si>
-    <t>企业应能禁止加载项目目录级的 MCP 和钩子</t>
+    <t>The enterprise shall be able to prohibit loading of project-directory-level MCP servers and hooks</t>
   </si>
   <si>
     <t>V5.6.1</t>
   </si>
   <si>
-    <t>V5.6 Skill、插件与 MCP 供应链</t>
-  </si>
-  <si>
-    <t>Skill、插件和 MCP Server 应经审核后才能安装</t>
-  </si>
-  <si>
-    <t>支持安装 Skill、插件或第三方 MCP 的平台</t>
+    <t>V5.6 Skill, Plugin, and MCP Supply Chain</t>
+  </si>
+  <si>
+    <t>Skills, plugins, and MCP servers shall be reviewed before they can be installed</t>
+  </si>
+  <si>
+    <t>Platforms that support installing skills, plugins, or third-party MCP servers</t>
   </si>
   <si>
     <t>V5.6.2</t>
   </si>
   <si>
-    <t>管理员应能维护允许安装的白名单，并能立即下架</t>
+    <t>Administrators shall be able to maintain an allowlist of permitted installations and to withdraw items immediately</t>
   </si>
   <si>
     <t>V5.6.3</t>
   </si>
   <si>
-    <t>应校验来源和签名并锁定版本，更新需重新审核</t>
+    <t>Source and signatures shall be verified and versions shall be pinned. Updates shall require re-review.</t>
   </si>
   <si>
     <t>V5.6.4</t>
   </si>
   <si>
-    <t>每个 Skill 或插件应声明所需权限，执行时超出声明的调用被拒绝</t>
+    <t>Each skill or plugin shall declare the permissions it requires, and invocations exceeding the declaration shall be rejected at execution</t>
   </si>
   <si>
     <t>V6.1.1</t>
   </si>
   <si>
-    <t>V6 上下文与不可信输入</t>
-  </si>
-  <si>
-    <t>V6.1 不可信内容标记</t>
-  </si>
-  <si>
-    <t>平台应将工具返回、检索结果、网页、邮件、文件和其他 Agent 的输出记为不可信内容，作为 V6.2 收紧规则的判断依据</t>
+    <t>V6 Context and Untrusted Input</t>
+  </si>
+  <si>
+    <t>V6.1 Untrusted Content Marking</t>
+  </si>
+  <si>
+    <t>The platform shall classify tool return values, retrieval results, web pages, emails, files, and the outputs of other agents as untrusted content, and use this classification as the basis for the tightening rules of V6.2</t>
   </si>
   <si>
     <t>V6.1.2</t>
   </si>
   <si>
-    <t>进入上下文的内容应标记来源，使策略检查能区分用户指令和不可信内容</t>
+    <t>Content entering the context shall be marked with its source so that policy checks can distinguish user instructions from untrusted content</t>
   </si>
   <si>
     <t>V6.1.3</t>
   </si>
   <si>
-    <t>平台策略和系统提示词应通过消息角色或分隔结构与不可信内容隔开，不拼接在同一段文本中</t>
+    <t>Platform policy and the system prompt shall be separated from untrusted content by message roles or delimiting structures, and shall not be concatenated within the same block of text</t>
   </si>
   <si>
     <t>V6.2.1</t>
   </si>
   <si>
-    <t>V6.2 接触不可信内容后的降级</t>
-  </si>
-  <si>
-    <t>会话接触不可信内容后，任何外发都应默认禁止，经审批后方可执行</t>
+    <t>V6.2 Downgrading After Exposure to Untrusted Content</t>
+  </si>
+  <si>
+    <t>After a session is exposed to untrusted content, all outbound transfers shall be denied by default and permitted only after approval</t>
   </si>
   <si>
     <t>V6.2.2</t>
   </si>
   <si>
-    <t>会话接触不可信内容后，对执行环境以外系统的写入和删除应转为审批，或限定在 V3.4.6 事先批准的计划范围内</t>
+    <t>After a session is exposed to untrusted content, writes and deletes to systems outside the execution environment shall require approval, or be limited to the plan pre-approved under V3.4.6</t>
   </si>
   <si>
     <t>V6.2.3</t>
   </si>
   <si>
-    <t>应定期用嵌入注入指令的网页、邮件、文档和工具返回，对 Agent 做红队测试</t>
+    <t>Red team tests shall be run periodically against agents, using web pages, emails, documents, and tool return values that embed injected instructions</t>
   </si>
   <si>
     <t>V6.2.4</t>
   </si>
   <si>
-    <t>高风险场景应先由没有工具权限的隔离模型处理不可信内容，只把结构化结果交给有权限的 Agent（如 Dual LLM 模式，或在其上增加控制流与数据流分离的 CaMeL）</t>
+    <t>In high-risk scenarios, untrusted content shall first be processed by an isolated model without tool permissions, and only structured results shall be passed to the agent that has permissions. Examples include the Dual LLM pattern, or CaMeL, which adds separation of control flow and data flow on top of it.</t>
   </si>
   <si>
     <t>V6.3.1</t>
   </si>
   <si>
-    <t>V6.3 系统提示词与配置</t>
-  </si>
-  <si>
-    <t>系统提示词、Agent 配置和 Skill 文件中不应包含凭证或密钥</t>
+    <t>V6.3 System Prompt and Configuration</t>
+  </si>
+  <si>
+    <t>System prompts, agent configurations, and skill files shall not contain credentials or keys</t>
   </si>
   <si>
     <t>V6.3.2</t>
   </si>
   <si>
-    <t>应假定系统提示词可能泄露，其中不应包含个人信息，也不应包含超出该 Agent 全部使用者共同可见范围的数据</t>
+    <t>The system prompt shall be assumed to be possibly leaked. It shall contain no personal information and no data that is not visible to every user of the agent.</t>
   </si>
   <si>
     <t>V6.3.3</t>
   </si>
   <si>
-    <t>Agent 配置和 Skill 文件在发布前应经过凭证扫描</t>
+    <t>Agent configurations and skill files shall undergo credential scanning before release</t>
   </si>
   <si>
     <t>V6.4.1</t>
   </si>
   <si>
-    <t>V6.4 多 Agent 级联</t>
-  </si>
-  <si>
-    <t>Agent 之间的消息应经平台转发并附带发送方身份，Agent 之间不直接通信</t>
-  </si>
-  <si>
-    <t>支持多 Agent 编排的平台</t>
+    <t>V6.4 Multi-Agent Cascading</t>
+  </si>
+  <si>
+    <t>Messages between agents shall be forwarded by the platform with the sender's identity attached. Agents shall not communicate directly with each other.</t>
+  </si>
+  <si>
+    <t>Platforms that support multi-agent orchestration</t>
   </si>
   <si>
     <t>V6.4.2</t>
   </si>
   <si>
-    <t>关键节点应校验上游输出的格式和取值范围，不合规的结果不再向下传递</t>
+    <t>Critical nodes shall validate the format and value range of upstream output, and results that do not conform shall not be passed further downstream</t>
   </si>
   <si>
     <t>V6.4.3</t>
   </si>
   <si>
-    <t>链路中异常输出或错误率超过阈值时，应熔断整条链路并告警</t>
+    <t>When anomalous output or the error rate in a chain exceeds a threshold, the entire chain shall be circuit-broken and an alert raised</t>
   </si>
   <si>
     <t>V7.1.1</t>
   </si>
   <si>
-    <t>V7 输出与可见性</t>
-  </si>
-  <si>
-    <t>V7.1 多人渠道</t>
-  </si>
-  <si>
-    <t>在多人渠道中，回复只能使用全部在场成员都有权访问的数据，否则按 V7.1.2 处理</t>
-  </si>
-  <si>
-    <t>支持群聊、频道、共享文档评论等多人渠道的平台</t>
+    <t>V7 Output and Visibility</t>
+  </si>
+  <si>
+    <t>V7.1 Multi-Party Channels</t>
+  </si>
+  <si>
+    <t>In a multi-party channel, replies may use only data that all present members are authorized to access. Otherwise, V7.1.2 applies.</t>
+  </si>
+  <si>
+    <t>Platforms that support multi-party channels such as group chats, channels, and comments on shared documents</t>
   </si>
   <si>
     <t>V7.1.2</t>
   </si>
   <si>
-    <t>超出部分在场成员权限的结果应只私信给触发者，渠道内只显示提示</t>
+    <t>Results that exceed the permissions of some present members shall be sent only by direct message to the user who triggered the request, and only a notice shall be displayed in the channel</t>
   </si>
   <si>
     <t>V7.1.3</t>
   </si>
   <si>
-    <t>渠道内有外部成员时，可展示内容的级别应进一步收紧</t>
+    <t>When external members are present in a channel, the classification level of content that may be displayed shall be further tightened</t>
   </si>
   <si>
     <t>V7.1.4</t>
   </si>
   <si>
-    <t>判断可展示内容时，应考虑之后加入的成员能翻看历史回复</t>
+    <t>When determining displayable content, it shall be considered that members who join later may view historical replies</t>
   </si>
   <si>
     <t>V7.2.1</t>
   </si>
   <si>
-    <t>V7.2 共享 Agent 会话隔离</t>
-  </si>
-  <si>
-    <t>共享 Agent 的会话应按用户隔离</t>
-  </si>
-  <si>
-    <t>多人共用同一个 Agent 的平台</t>
+    <t>V7.2 Isolation of Shared Agent Sessions</t>
+  </si>
+  <si>
+    <t>Sessions of a shared agent shall be isolated by user</t>
+  </si>
+  <si>
+    <t>Platforms where multiple people share the same agent</t>
   </si>
   <si>
     <t>V7.2.2</t>
   </si>
   <si>
-    <t>数据层</t>
-  </si>
-  <si>
-    <t>个人上下文与团队共享知识应分开存放，检索时按当前用户作出授权判定</t>
+    <t>Data layer</t>
+  </si>
+  <si>
+    <t>Personal context and team-shared knowledge shall be stored separately, and retrieval shall make authorization decisions based on the current user</t>
   </si>
   <si>
     <t>V7.3.1</t>
   </si>
   <si>
-    <t>V7.3 会话转交</t>
-  </si>
-  <si>
-    <t>会话转交前应按接收人的权限检查已有上下文</t>
-  </si>
-  <si>
-    <t>支持会话转交或人工接管的平台</t>
+    <t>V7.3 Session Handover</t>
+  </si>
+  <si>
+    <t>Before a session is handed over, its existing context shall be checked against the recipient's permissions</t>
+  </si>
+  <si>
+    <t>Platforms that support session handover or human takeover</t>
   </si>
   <si>
     <t>V7.3.2</t>
   </si>
   <si>
-    <t>超出接收人权限的内容应脱敏或移除后再转交</t>
+    <t>Content that exceeds the recipient's permissions shall be redacted or removed before the handover</t>
   </si>
   <si>
     <t>V7.4.1</t>
   </si>
   <si>
-    <t>V7.4 输出渲染</t>
-  </si>
-  <si>
-    <t>平台发往任何渠道的回复中，指向白名单以外域名的图片和资源应在发送前移除，或改为不自动加载的链接</t>
+    <t>V7.4 Output Rendering</t>
+  </si>
+  <si>
+    <t>In replies the platform sends to any channel, images and resources that point to domains outside the allowlist shall be removed before sending, or converted to links that do not load automatically</t>
   </si>
   <si>
     <t>V7.4.2</t>
   </si>
   <si>
-    <t>回复中的 HTML 和 Markdown 应在渲染前净化，去除脚本和事件属性</t>
+    <t>HTML and Markdown in replies shall be sanitized before rendering, removing scripts and event attributes</t>
   </si>
   <si>
     <t>V7.4.3</t>
   </si>
   <si>
-    <t>回复中的链接应显示真实的目标地址</t>
+    <t>Links in replies shall display the real destination address</t>
   </si>
   <si>
     <t>V7.5.1</t>
   </si>
   <si>
-    <t>V7.5 输出数据防泄漏</t>
-  </si>
-  <si>
-    <t>回复和外发内容中出现凭证或密钥时应被拦截</t>
+    <t>V7.5 Output Data Leakage Prevention</t>
+  </si>
+  <si>
+    <t>When credentials or keys appear in replies or outbound content, they shall be blocked</t>
   </si>
   <si>
     <t>V7.5.2</t>
   </si>
   <si>
-    <t>回复、文件下载和外发的内容应经过敏感数据检测</t>
+    <t>Replies, file downloads, and outbound content shall undergo sensitive data detection</t>
   </si>
   <si>
     <t>V7.5.3</t>
   </si>
   <si>
-    <t>命中个人信息等敏感数据时，应按策略脱敏或转为审批</t>
+    <t>When sensitive data such as personal information is detected, it shall be redacted according to policy, or the output shall require approval</t>
   </si>
   <si>
     <t>V7.5.4</t>
   </si>
   <si>
-    <t>会话读取过非公开数据后，任何外发都应默认禁止，经审批后方可执行</t>
+    <t>After a session has read non-public data, all outbound transfers shall be denied by default and permitted only after approval</t>
   </si>
   <si>
     <t>V7.6.1</t>
   </si>
   <si>
-    <t>V7.6 代发消息</t>
-  </si>
-  <si>
-    <t>发往企业外部收件人的消息应经过审批</t>
-  </si>
-  <si>
-    <t>支持以用户名义发送邮件、IM 或公告的平台</t>
+    <t>V7.6 Messages Sent on Behalf of a User</t>
+  </si>
+  <si>
+    <t>Messages sent to recipients outside the enterprise shall be approved</t>
+  </si>
+  <si>
+    <t>Platforms that send email, IM messages, or announcements in the user's name</t>
   </si>
   <si>
     <t>V7.6.2</t>
   </si>
   <si>
-    <t>代发的默认方式应为生成草稿，由用户确认后发出</t>
+    <t>The default mode for sending on behalf of a user shall be to generate a draft, which is sent after the user confirms</t>
   </si>
   <si>
     <t>V7.6.3</t>
   </si>
   <si>
-    <t>由 Agent 代发的消息应带有可识别的代发标识</t>
+    <t>Messages sent by an agent on behalf of a user shall carry a recognizable sent-on-behalf-of identifier</t>
   </si>
   <si>
     <t>V8.1.1</t>
   </si>
   <si>
-    <t>V8 数据、记忆与产出物</t>
-  </si>
-  <si>
-    <t>V8.1 检索授权</t>
-  </si>
-  <si>
-    <t>检索结果应按源系统的访问控制过滤，可将访问控制列表同步到每个文本块（chunk），或在检索时回源校验</t>
-  </si>
-  <si>
-    <t>支持 RAG 或知识库检索的平台</t>
+    <t>V8 Data, Memory, and Output Artifacts</t>
+  </si>
+  <si>
+    <t>V8.1 Retrieval Authorization</t>
+  </si>
+  <si>
+    <t>Retrieval results shall be filtered by the access controls of the source system. Access control lists may be synchronized to each text chunk, or verified back against the source at retrieval time.</t>
+  </si>
+  <si>
+    <t>Platforms that support RAG or knowledge base retrieval</t>
   </si>
   <si>
     <t>V8.1.2</t>
   </si>
   <si>
-    <t>应在检索阶段按当前用户过滤结果，而不是生成回答后再删除</t>
+    <t>Results shall be filtered by the current user at the retrieval stage, rather than deleted after the answer has been generated</t>
   </si>
   <si>
     <t>V8.1.3</t>
   </si>
   <si>
-    <t>源系统撤销权限后，应在约定时长内反映到检索结果，并监控同步延迟</t>
+    <t>After permissions are revoked in the source system, the change shall be reflected in retrieval results within an agreed period, and synchronization latency shall be monitored</t>
   </si>
   <si>
     <t>V8.2.1</t>
   </si>
   <si>
-    <t>V8.2 数据库查询</t>
-  </si>
-  <si>
-    <t>Agent 查询数据库应以用户身份连接，或由平台注入该用户的行级、列级策略</t>
-  </si>
-  <si>
-    <t>Agent 直接查询业务数据库的平台</t>
+    <t>V8.2 Database Queries</t>
+  </si>
+  <si>
+    <t>When an agent queries a database, it shall connect under the user's identity, or the platform shall inject that user's row-level and column-level policies</t>
+  </si>
+  <si>
+    <t>Platforms where agents query business databases directly</t>
   </si>
   <si>
     <t>V8.2.2</t>
   </si>
   <si>
-    <t>Agent 使用的数据库连接默认应为只读</t>
+    <t>Database connections used by agents shall be read-only by default</t>
   </si>
   <si>
     <t>V8.2.3</t>
   </si>
   <si>
-    <t>单次查询返回的行数应设上限</t>
+    <t>The number of rows returned by a single query shall be capped</t>
   </si>
   <si>
     <t>V8.3.1</t>
   </si>
   <si>
-    <t>V8.3 记忆隔离</t>
-  </si>
-  <si>
-    <t>记忆应记录来源用户和权限标签</t>
-  </si>
-  <si>
-    <t>支持长期记忆或知识沉淀的平台</t>
+    <t>V8.3 Memory Isolation</t>
+  </si>
+  <si>
+    <t>Memory shall record the source user and permission labels</t>
+  </si>
+  <si>
+    <t>Platforms that support long-term memory or knowledge accumulation</t>
   </si>
   <si>
     <t>V8.3.2</t>
   </si>
   <si>
-    <t>检索记忆时应按当前用户过滤，一个用户的个人记忆不能出现在其他用户的会话中</t>
+    <t>When memory is retrieved, results shall be filtered by the current user, and one user's personal memory shall not appear in another user's session</t>
   </si>
   <si>
     <t>V8.3.3</t>
   </si>
   <si>
-    <t>个人内容沉淀为团队共享知识前应经过审核</t>
+    <t>Personal content shall be reviewed before it is accumulated into team-shared knowledge</t>
   </si>
   <si>
     <t>V8.4.1</t>
   </si>
   <si>
-    <t>V8.4 记忆与知识投毒</t>
-  </si>
-  <si>
-    <t>写入记忆和知识库的内容应标记来源和可信度</t>
+    <t>V8.4 Memory and Knowledge Poisoning</t>
+  </si>
+  <si>
+    <t>Content written into memory and knowledge bases shall be marked with its source and credibility</t>
   </si>
   <si>
     <t>V8.4.2</t>
   </si>
   <si>
-    <t>来自不可信内容的沉淀应经人工审核后才能被检索</t>
+    <t>Accumulations originating from untrusted content shall be reviewed manually before they can be retrieved</t>
   </si>
   <si>
     <t>V8.4.3</t>
   </si>
   <si>
-    <t>检索出的记忆应作为数据交给模型，不作为系统指令</t>
+    <t>Retrieved memory shall be provided to the model as data, not as system instructions</t>
   </si>
   <si>
     <t>V8.4.4</t>
   </si>
   <si>
-    <t>应支持按来源回溯，并批量清除记忆和知识条目</t>
+    <t>The platform shall support tracing memory and knowledge entries back to their source and removing them in bulk</t>
   </si>
   <si>
     <t>V8.5.1</t>
   </si>
   <si>
-    <t>V8.5 产出物</t>
-  </si>
-  <si>
-    <t>产出物应继承其来源中的最高数据级别，并记录来源</t>
+    <t>V8.5 Output Artifacts</t>
+  </si>
+  <si>
+    <t>Output artifacts shall inherit the highest data classification level among their sources and shall record their sources</t>
   </si>
   <si>
     <t>V8.5.2</t>
   </si>
   <si>
-    <t>共享产出物时，应检查接收人对来源数据的权限</t>
+    <t>When an output artifact is shared, the recipient's permissions on the source data shall be checked</t>
   </si>
   <si>
     <t>V8.5.3</t>
   </si>
   <si>
-    <t>对敏感维度的聚合和统计请求应转为审批</t>
+    <t>Aggregation and statistics requests on sensitive dimensions shall require approval</t>
   </si>
   <si>
     <t>V8.6.1</t>
   </si>
   <si>
-    <t>V8.6 缓存与留存</t>
-  </si>
-  <si>
-    <t>缓存的检索结果和回答应带权限标签，权限变更后失效</t>
+    <t>V8.6 Caching and Retention</t>
+  </si>
+  <si>
+    <t>Cached retrieval results and answers shall carry permission labels and shall be invalidated when permissions change</t>
   </si>
   <si>
     <t>V8.6.2</t>
   </si>
   <si>
-    <t>历史会话应按当前权限展示，已收回权限的内容不再显示</t>
+    <t>Historical sessions shall be displayed according to current permissions, and content whose permissions have been revoked shall no longer be displayed</t>
   </si>
   <si>
     <t>V8.6.3</t>
   </si>
   <si>
-    <t>应为会话、记忆和审计分别设置保留期限</t>
+    <t>Retention periods shall be set separately for sessions, memory, and audit records</t>
   </si>
   <si>
     <t>V8.6.4</t>
   </si>
   <si>
-    <t>用户离职后，其托管凭证应在约定时间内删除，个人记忆按策略删除或移交</t>
+    <t>After a user leaves, their managed credentials shall be deleted within an agreed time, and personal memory shall be deleted or transferred according to policy</t>
   </si>
   <si>
     <t>V8.7.1</t>
   </si>
   <si>
-    <t>V8.7 模型路由</t>
-  </si>
-  <si>
-    <t>应按数据分级配置每类数据可以发往的模型，敏感数据只发往本地或指定模型</t>
-  </si>
-  <si>
-    <t>接入多个模型的平台。对话数据用于评估和微调属于模型训练的数据治理，参见 OWASP AISVS 的 C1 和 C3</t>
+    <t>V8.7 Model Routing</t>
+  </si>
+  <si>
+    <t>The models to which each category of data may be sent shall be configured according to data classification. Sensitive data shall be sent only to local or designated models.</t>
+  </si>
+  <si>
+    <t>Platforms that connect to multiple models. Use of conversation data for evaluation and fine-tuning is model training data governance; see OWASP AISVS C1 and C3.</t>
   </si>
   <si>
     <t>V8.7.2</t>
   </si>
   <si>
-    <t>发往未授权模型的敏感数据应被拦截</t>
+    <t>Sensitive data destined for unauthorized models shall be blocked</t>
   </si>
   <si>
     <t>V9.1.1</t>
   </si>
   <si>
-    <t>V9 生命周期与治理</t>
-  </si>
-  <si>
-    <t>V9.1 Agent 登记与发布</t>
-  </si>
-  <si>
-    <t>创建、发布和下线 Agent 应分别授权</t>
+    <t>V9 Lifecycle and Governance</t>
+  </si>
+  <si>
+    <t>V9.1 Agent Registration and Publication</t>
+  </si>
+  <si>
+    <t>Creating, publishing, and decommissioning agents shall each be separately authorized</t>
   </si>
   <si>
     <t>V9.1.2</t>
   </si>
   <si>
-    <t>Agent 发布前应经过审核，未指定负责人的 Agent 不能发布</t>
+    <t>Agents shall be reviewed before publication, and agents without a designated owner shall not be published</t>
   </si>
   <si>
     <t>V9.1.3</t>
   </si>
   <si>
-    <t>平台应能列出全部已发布的 Agent，以及各自的授权范围、连接和负责人</t>
+    <t>The platform shall be able to list all published agents, along with their authorization scopes, connections, and owners</t>
   </si>
   <si>
     <t>V9.1.4</t>
   </si>
   <si>
-    <t>Agent 登记信息应包含所用模型及版本、Harness 版本和已连接的工具，变更时同步更新</t>
+    <t>Agent registration information shall include the models and versions used, the harness version, and the connected tools, and shall be updated synchronously when any of them change</t>
   </si>
   <si>
     <t>V9.2.1</t>
   </si>
   <si>
-    <t>V9.2 连接器与凭证绑定</t>
-  </si>
-  <si>
-    <t>为 Agent 绑定连接器应需要相应权限，且不能超出该 Agent 登记的授权范围</t>
+    <t>V9.2 Connector and Credential Binding</t>
+  </si>
+  <si>
+    <t>Binding connectors to an agent shall require the corresponding permission, and shall not exceed the authorization scope registered for that agent</t>
   </si>
   <si>
     <t>V9.2.2</t>
   </si>
   <si>
-    <t>凭证绑定后，绑定人不应能再查看或导出其明文</t>
+    <t>After credentials are bound, the binder shall no longer be able to view or export their plaintext</t>
   </si>
   <si>
     <t>V9.2.3</t>
   </si>
   <si>
-    <t>连接器的绑定和变更应记录审计</t>
+    <t>Binding and changes of connectors shall be recorded in the audit log</t>
   </si>
   <si>
     <t>V9.3.1</t>
   </si>
   <si>
-    <t>V9.3 配置变更</t>
-  </si>
-  <si>
-    <t>修改 Agent 的系统提示词、工具、授权范围和策略应经过审批</t>
+    <t>V9.3 Configuration Changes</t>
+  </si>
+  <si>
+    <t>Changes to an agent's system prompt, tools, authorization scope, and policies shall be approved</t>
   </si>
   <si>
     <t>V9.3.2</t>
   </si>
   <si>
-    <t>未经审批的配置变更不应生效</t>
+    <t>Configuration changes that have not been approved shall not take effect</t>
   </si>
   <si>
     <t>V9.3.3</t>
   </si>
   <si>
-    <t>配置应保留版本记录，可回滚到任一历史版本</t>
+    <t>Configurations shall retain version records and be rollbackable to any historical version</t>
   </si>
   <si>
     <t>V9.3.4</t>
   </si>
   <si>
-    <t>更换 Agent 使用的模型或模型版本，应按配置变更审批，并重新评估其行为</t>
+    <t>Replacing the model or model version used by an agent shall be approved as a configuration change, and its behavior shall be reassessed</t>
   </si>
   <si>
     <t>V9.3.5</t>
   </si>
   <si>
-    <t>风险分级、凭证目标绑定、出口放行清单和托管策略等全局策略的变更，应限定专门角色执行，并记录操作人、时间和变更前后内容</t>
+    <t>Changes to global policies, such as risk classification, credential target binding, egress allowlists, and managed policies, shall be restricted to dedicated roles, and the platform shall record the operator, the time, and the content before and after each change</t>
   </si>
   <si>
     <t>V9.3.6</t>
   </si>
   <si>
-    <t>上述全局策略的变更应经第二人审批后生效</t>
+    <t>Changes to the above global policies shall take effect only after approval by a second person</t>
   </si>
   <si>
     <t>V9.4.1</t>
   </si>
   <si>
-    <t>V9.4 生命周期与权限复核</t>
-  </si>
-  <si>
-    <t>负责人离职或转岗时，其名下 Agent 应进入待转交状态，限期未转交则自动停用</t>
+    <t>V9.4 Lifecycle and Permission Review</t>
+  </si>
+  <si>
+    <t>When an owner leaves or changes roles, the agents under their name shall enter a pending-handover state. If they are not handed over within the deadline, they shall be disabled automatically.</t>
   </si>
   <si>
     <t>V9.4.2</t>
   </si>
   <si>
-    <t>应定期复核 Agent 的连接和权限，到期未确认的权限自动收回</t>
+    <t>Agent connections and permissions shall be reviewed periodically, and permissions not confirmed by their due date shall be withdrawn automatically</t>
   </si>
   <si>
     <t>V9.4.3</t>
   </si>
   <si>
-    <t>长期未使用的 Agent 应被识别并下线</t>
+    <t>Agents that have been unused for a long period shall be identified and decommissioned</t>
   </si>
   <si>
     <t>V9.5.1</t>
   </si>
   <si>
-    <t>V9.5 影子 Agent 发现</t>
-  </si>
-  <si>
-    <t>应通过 IdP 的 OAuth 授权记录，发现员工自行接入、未经登记的 Agent</t>
+    <t>V9.5 Shadow Agent Discovery</t>
+  </si>
+  <si>
+    <t>Agents that employees have connected on their own initiative without registration shall be discovered through the OAuth authorization records of the IdP</t>
   </si>
   <si>
     <t>V9.5.2</t>
   </si>
   <si>
-    <t>发现的未登记 Agent 应在约定时间内登记纳管或封禁</t>
+    <t>Discovered unregistered agents shall be registered and brought under management, or blocked, within an agreed time</t>
   </si>
   <si>
     <t>V9.5.3</t>
   </si>
   <si>
-    <t>应结合终端和网络检测，发现端侧和浏览器中的未登记 Agent</t>
+    <t>Unregistered agents on endpoints and in browsers shall be discovered through combined endpoint and network detection</t>
   </si>
   <si>
     <t>V9.6.1</t>
   </si>
   <si>
-    <t>V9.6 工作空间隔离</t>
-  </si>
-  <si>
-    <t>数据、知识库、凭证和 Agent 应按工作空间隔离</t>
+    <t>V9.6 Workspace Isolation</t>
+  </si>
+  <si>
+    <t>Data, knowledge bases, credentials, and agents shall be isolated by workspace</t>
   </si>
   <si>
     <t>V9.6.2</t>
   </si>
   <si>
-    <t>跨工作空间访问应经过显式授权</t>
+    <t>Cross-workspace access shall require explicit authorization</t>
   </si>
   <si>
     <t>V9.6.3</t>
   </si>
   <si>
-    <t>以 SaaS 交付时，不同租户的数据、凭证和执行环境应完全隔离</t>
+    <t>When delivered as SaaS, the data, credentials, and execution environments of different tenants shall be fully isolated</t>
   </si>
   <si>
     <t>V9.7.1</t>
   </si>
   <si>
-    <t>V9.7 提供方人员访问</t>
-  </si>
-  <si>
-    <t>提供方对客户环境和数据的访问应默认关闭，开启需客户审批并限定时长</t>
+    <t>V9.7 Provider Personnel Access</t>
+  </si>
+  <si>
+    <t>The provider's access to customer environments and data shall be disabled by default. Enabling it shall require customer approval and be limited in duration.</t>
   </si>
   <si>
     <t>V9.7.2</t>
   </si>
   <si>
-    <t>提供方的每次访问都应全程审计，审计记录对客户可见</t>
+    <t>Each provider access shall be fully audited end to end, and the audit records shall be visible to the customer</t>
   </si>
   <si>
     <t>V9.7.3</t>
   </si>
   <si>
-    <t>遥测数据应只包含公开清单中的字段，且客户可以关闭</t>
+    <t>Telemetry data shall include only fields on a published inventory, and customers may disable it</t>
   </si>
   <si>
     <t>V9.7.4</t>
   </si>
   <si>
-    <t>私有化部署的登录和授权判定不应依赖提供方的在线服务</t>
+    <t>Login and authorization decisions for private deployments shall not depend on the provider's online services</t>
   </si>
   <si>
     <t>V10.1.1</t>
   </si>
   <si>
-    <t>V10 审计、检测与响应</t>
-  </si>
-  <si>
-    <t>V10.1 审计记录</t>
-  </si>
-  <si>
-    <t>每次工具调用都应记录发起用户、执行的 Agent、委托链、触发源、工具参数和结果状态</t>
+    <t>V10 Audit, Detection, and Response</t>
+  </si>
+  <si>
+    <t>V10.1 Audit Records</t>
+  </si>
+  <si>
+    <t>For each tool invocation, the platform shall record the initiating user, the executing agent, the delegation chain, the trigger source, the tool parameters, and the result status</t>
   </si>
   <si>
     <t>V10.1.2</t>
   </si>
   <si>
-    <t>经过审批的操作应记录审批人、审批内容和审批时间</t>
+    <t>For approved operations, the platform shall record the approver, the approval content, and the approval time</t>
   </si>
   <si>
     <t>V10.1.3</t>
   </si>
   <si>
-    <t>审计应记录进入上下文的不可信内容的来源，使事后能判断操作是否由注入引起</t>
+    <t>Audit shall record the source of untrusted content entering the context, so that it can later be determined whether an operation was caused by injection</t>
   </si>
   <si>
     <t>V10.1.4</t>
   </si>
   <si>
-    <t>审计应能导出到企业 SIEM</t>
+    <t>The platform shall be able to export audit records to the enterprise SIEM</t>
   </si>
   <si>
     <t>V10.1.5</t>
   </si>
   <si>
-    <t>审计日志应以只追加方式写入与平台运维隔离的存储，或以哈希链等方式使篡改可被发现</t>
+    <t>Audit logs shall be written to append-only storage isolated from platform operations, or tampering shall be detectable through means such as hash chains</t>
   </si>
   <si>
     <t>V10.1.6</t>
   </si>
   <si>
-    <t>审计记录应以密码学方式绑定执行它的 Agent 身份，以及授权它的用户或审批，保证不可抵赖</t>
+    <t>Audit records shall be cryptographically bound to the identity of the agent that executed them and to the user or approval that authorized them, to ensure non-repudiation</t>
   </si>
   <si>
     <t>V10.2.1</t>
   </si>
   <si>
-    <t>V10.2 审计数据保护与调阅</t>
-  </si>
-  <si>
-    <t>管理员调阅审计或对话的行为本身应记录审计</t>
+    <t>V10.2 Audit Data Protection and Retrieval</t>
+  </si>
+  <si>
+    <t>When administrators retrieve audit records or conversations, the act of retrieval itself shall be recorded in the audit log</t>
   </si>
   <si>
     <t>V10.2.2</t>
   </si>
   <si>
-    <t>审计日志中的敏感字段应脱敏存储，或按角色控制可见</t>
+    <t>Sensitive fields in audit logs shall be stored redacted, or their visibility shall be controlled by role</t>
   </si>
   <si>
     <t>V10.2.3</t>
   </si>
   <si>
-    <t>管理员调阅用户与 Agent 的对话应经过审批</t>
+    <t>When administrators retrieve conversations between users and agents, the retrieval shall be approved</t>
   </si>
   <si>
     <t>V10.2.4</t>
   </si>
   <si>
-    <t>审计记录在保留期内不应能被删除</t>
+    <t>Audit records shall not be deletable during the retention period</t>
   </si>
   <si>
     <t>V10.3.1</t>
   </si>
   <si>
-    <t>V10.3 行为检测</t>
-  </si>
-  <si>
-    <t>策略拒绝、审批拒绝、凭证目标不匹配等事件应实时告警</t>
+    <t>V10.3 Behavioral Detection</t>
+  </si>
+  <si>
+    <t>Events such as policy denials, approval rejections, and credential target mismatches shall generate real-time alerts</t>
   </si>
   <si>
     <t>V10.3.2</t>
   </si>
   <si>
-    <t>应能按 Agent、用户和委托链检索并关联告警</t>
+    <t>The platform shall be able to retrieve and correlate alerts by agent, user, and delegation chain</t>
   </si>
   <si>
     <t>V10.3.3</t>
   </si>
   <si>
-    <t>应为每个 Agent 建立行为基线（调用频率、工具分布、数据量），偏离时告警</t>
+    <t>A behavioral baseline (invocation frequency, tool distribution, data volume) shall be established for each agent, and deviations shall trigger alerts</t>
   </si>
   <si>
     <t>V10.4.1</t>
   </si>
   <si>
-    <t>V10.4 权限撤销与紧急停用</t>
-  </si>
-  <si>
-    <t>IdP 禁用用户或降权后，相关调用应在约定时长内（如 5 分钟）全部被拒</t>
+    <t>V10.4 Permission Revocation and Emergency Deactivation</t>
+  </si>
+  <si>
+    <t>After the IdP disables a user or downgrades their permissions, related invocations shall all be rejected within an agreed period (such as 5 minutes)</t>
   </si>
   <si>
     <t>V10.4.2</t>
   </si>
   <si>
-    <t>权限缓存应设时长上限</t>
+    <t>Permission caches shall have an upper limit on their duration</t>
   </si>
   <si>
     <t>V10.4.3</t>
   </si>
   <si>
-    <t>应能通过单次操作停用单个 Agent，停用时网关停止为其注入凭证，并吊销其刷新令牌、中止运行中的任务、结束会话</t>
+    <t>The platform shall be able to deactivate an individual agent in a single operation. Deactivation shall stop the gateway from injecting credentials for the agent, revoke its refresh tokens, abort its running tasks, and end its sessions</t>
   </si>
   <si>
     <t>V10.4.4</t>
   </si>
   <si>
-    <t>平台应接收 IdP 的会话撤销事件（如 CAEP），收到后立即生效</t>
+    <t>The platform shall receive session revocation events from the IdP (such as CAEP) and shall take effect immediately upon receipt</t>
   </si>
   <si>
     <t>V10.4.5</t>
   </si>
   <si>
-    <t>应能按负责人、工作空间或连接器批量停用 Agent</t>
+    <t>The platform shall be able to deactivate agents in bulk by owner, workspace, or connector</t>
   </si>
   <si>
     <t>V10.5.1</t>
   </si>
   <si>
-    <t>V10.5 紧急访问</t>
-  </si>
-  <si>
-    <t>应预置在 IdP 不可用时也能登录管理面的紧急访问账号</t>
+    <t>V10.5 Emergency Access</t>
+  </si>
+  <si>
+    <t>Break-glass accounts that can log in to the management plane even when the IdP is unavailable shall be pre-provisioned</t>
   </si>
   <si>
     <t>V10.5.2</t>
   </si>
   <si>
-    <t>紧急访问账号的凭证应分割保管、双人控制，使用即告警并全程审计</t>
+    <t>Credentials for break-glass accounts shall be split-custodied and under dual control, with an alert on each use and full audit</t>
   </si>
   <si>
     <t>V10.6.1</t>
   </si>
   <si>
-    <t>V10.6 事件响应与恢复</t>
-  </si>
-  <si>
-    <t>应制定 Agent 被注入或被攻陷时的响应流程，覆盖停用、凭证轮换和影响范围排查</t>
+    <t>V10.6 Incident Response and Recovery</t>
+  </si>
+  <si>
+    <t>A response procedure shall be established for when an agent is injected or compromised, covering deactivation, credential rotation, and investigation of the impact scope</t>
   </si>
   <si>
     <t>V10.6.2</t>
   </si>
   <si>
-    <t>应能按会话或委托链还原 Agent 在指定时段内的全部操作，用于确定影响范围</t>
+    <t>The platform shall be able to reconstruct all of an agent's operations within a specified period, by session or by delegation chain, to determine the scope of impact</t>
   </si>
   <si>
     <t>V10.6.3</t>
   </si>
   <si>
-    <t>写入类操作应可撤销，或在执行前保留可回滚的快照</t>
-  </si>
-  <si>
-    <t>评估进度</t>
-  </si>
-  <si>
-    <t>数字由公式从「评估表」实时计算。目标等级内的条目 = 该等级及以下全部条目；满足率 = 已满足 ÷（条目数 − 不适用）；未评估按未满足计。</t>
-  </si>
-  <si>
-    <t>目标等级</t>
-  </si>
-  <si>
-    <t>条目数</t>
-  </si>
-  <si>
-    <t>已满足</t>
-  </si>
-  <si>
-    <t>部分满足</t>
-  </si>
-  <si>
-    <t>未满足</t>
-  </si>
-  <si>
-    <t>不适用</t>
-  </si>
-  <si>
-    <t>满足率</t>
-  </si>
-  <si>
-    <t>结论</t>
-  </si>
-  <si>
-    <t>达到 L1</t>
-  </si>
-  <si>
-    <t>达到 L2</t>
-  </si>
-  <si>
-    <t>达到 L3</t>
-  </si>
-  <si>
-    <t>下面三张表按此目标等级统计 ▸</t>
-  </si>
-  <si>
-    <t>（下拉切换 L1 / L2 / L3）</t>
+    <t>Write operations shall be reversible, or a rollback snapshot shall be retained before execution</t>
+  </si>
+  <si>
+    <t>Assessment Progress</t>
+  </si>
+  <si>
+    <t>Figures are calculated live by formulas from “Assessment Sheet”. Items within a target level = all items at that level and below; conformance rate = met ÷ (items − not applicable); not assessed counts as unmet.</t>
+  </si>
+  <si>
+    <t>Target Level</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>Partially Met</t>
+  </si>
+  <si>
+    <t>Unmet</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Conformance Rate</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Reach L1</t>
+  </si>
+  <si>
+    <t>Reach L2</t>
+  </si>
+  <si>
+    <t>Reach L3</t>
+  </si>
+  <si>
+    <t>The three tables below are calculated for this target level ▸</t>
+  </si>
+  <si>
+    <t>(switch between L1 / L2 / L3 in the drop-down)</t>
   </si>
   <si>
     <t>按架构组件</t>
@@ -1883,28 +1883,28 @@
     <t>架构组件</t>
   </si>
   <si>
-    <t>L2 新增</t>
-  </si>
-  <si>
-    <t>L3 新增</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>目标内条目</t>
-  </si>
-  <si>
-    <t>达成等级</t>
-  </si>
-  <si>
-    <t>按章</t>
-  </si>
-  <si>
-    <t>组件 × 章（全部等级的条目数）</t>
-  </si>
-  <si>
-    <t>组件</t>
+    <t>New in L2</t>
+  </si>
+  <si>
+    <t>New in L3</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Items in target</t>
+  </si>
+  <si>
+    <t>Achieved Level</t>
+  </si>
+  <si>
+    <t>By chapter</t>
+  </si>
+  <si>
+    <t>Component × Chapter (item counts across all levels)</t>
+  </si>
+  <si>
+    <t>Component</t>
   </si>
   <si>
     <t>V1</t>
@@ -1937,268 +1937,268 @@
     <t>V10</t>
   </si>
   <si>
-    <t>颜色越深，该章越依赖这个组件落地。</t>
-  </si>
-  <si>
-    <t>差距清单（目标等级 L2）</t>
-  </si>
-  <si>
-    <t>导出时按目标等级内、状态不是「已满足」或「不适用」的要求生成，按等级和编号排序。在评估表里改状态后，这一页不会自动更新，请重新导出。</t>
-  </si>
-  <si>
-    <t>架构视角</t>
-  </si>
-  <si>
-    <t>对应基线第 4 章。落点组件指主要负责实现或强制执行该要求的组件，多个组件配合时取最主要的一个。</t>
-  </si>
-  <si>
-    <t>职责</t>
-  </si>
-  <si>
-    <t>信任假设</t>
-  </si>
-  <si>
-    <t>企业 IdP、目录、SCIM，签发用户、Agent 和工作负载身份</t>
-  </si>
-  <si>
-    <t>可信</t>
-  </si>
-  <si>
-    <t>Web、IM、邮件、IDE、API 等入口，负责身份映射和输出的可见范围</t>
-  </si>
-  <si>
-    <t>可信；经渠道进入的内容不可信</t>
-  </si>
-  <si>
-    <t>Agent 循环、上下文管理、工具层、安全控制、编排、扩展接口</t>
-  </si>
-  <si>
-    <t>平台托管时可信；在员工终端运行时不可信，按 V5.4</t>
-  </si>
-  <si>
-    <t>计算有效权限、判定风险等级、决定是否审批</t>
-  </si>
-  <si>
-    <t>统一出口，注入凭证、校验目标、限流、吊销；凭证库归属于此</t>
-  </si>
-  <si>
-    <t>被访问的 SaaS、内部 API、MCP Server、数据库</t>
-  </si>
-  <si>
-    <t>自行作出授权判定；返回内容不可信</t>
-  </si>
-  <si>
-    <t>知识库、RAG、记忆、产出物</t>
-  </si>
-  <si>
-    <t>可信；存储的内容可能被污染，按不可信内容处理</t>
-  </si>
-  <si>
-    <t>执行代码、命令、文件和浏览器操作</t>
-  </si>
-  <si>
-    <t>不可信，可能被攻陷</t>
-  </si>
-  <si>
-    <t>Agent 登记、连接器、托管策略、生命周期</t>
-  </si>
-  <si>
-    <t>记录、调阅、导出与留存，以及检测与响应</t>
-  </si>
-  <si>
-    <t>模型不承担任何控制：它的输出只是请求，相关要求落在 Harness 上。</t>
-  </si>
-  <si>
-    <t>一次工具调用的检查点</t>
-  </si>
-  <si>
-    <t>步骤</t>
-  </si>
-  <si>
-    <t>检查点</t>
-  </si>
-  <si>
-    <t>发生了什么</t>
-  </si>
-  <si>
-    <t>负责组件</t>
-  </si>
-  <si>
-    <t>相关要求</t>
-  </si>
-  <si>
-    <t>入口认证</t>
-  </si>
-  <si>
-    <t>渠道账号映射到企业身份</t>
-  </si>
-  <si>
-    <t>交互渠道、身份层</t>
+    <t>The darker the color, the more the chapter depends on this component for implementation.</t>
+  </si>
+  <si>
+    <t>Gap List (target level L2)</t>
+  </si>
+  <si>
+    <t>Generated at export from the requirements within the target level whose status is neither “Met” nor “Not applicable”, sorted by level and ID. This sheet does not update automatically when you change statuses in the assessment sheet; export again to refresh it.</t>
+  </si>
+  <si>
+    <t>Architecture View</t>
+  </si>
+  <si>
+    <t>Corresponds to Chapter 4 of the baseline. The enforcement component is the component primarily responsible for implementing or enforcing a requirement; when several components work together, the main one is listed.</t>
+  </si>
+  <si>
+    <t>Responsibilities</t>
+  </si>
+  <si>
+    <t>Trust Assumption</t>
+  </si>
+  <si>
+    <t>Enterprise IdP, directory, and SCIM; issues user, agent, and workload identities</t>
+  </si>
+  <si>
+    <t>Trusted</t>
+  </si>
+  <si>
+    <t>Web, IM, email, IDE, API, and other entry points; responsible for identity mapping and the visibility scope of output</t>
+  </si>
+  <si>
+    <t>Trusted; content arriving through the channel is untrusted</t>
+  </si>
+  <si>
+    <t>Agent loop, context management, tool layer, security controls, orchestration, extension interfaces</t>
+  </si>
+  <si>
+    <t>Trusted when platform-hosted; untrusted when running on employee endpoints, per V5.4</t>
+  </si>
+  <si>
+    <t>Computes effective permissions, determines risk levels, and decides whether approval is required</t>
+  </si>
+  <si>
+    <t>Unified egress; injects credentials, validates targets, rate-limits, and revokes; the credential store belongs here</t>
+  </si>
+  <si>
+    <t>SaaS, internal APIs, MCP servers, and databases being accessed</t>
+  </si>
+  <si>
+    <t>Makes its own authorization decisions; returned content is untrusted</t>
+  </si>
+  <si>
+    <t>Knowledge bases, RAG, memory, output artifacts</t>
+  </si>
+  <si>
+    <t>Trusted; stored content may be poisoned and is handled as untrusted content</t>
+  </si>
+  <si>
+    <t>Executes code, commands, files, and browser operations</t>
+  </si>
+  <si>
+    <t>Untrusted; may be compromised</t>
+  </si>
+  <si>
+    <t>Agent registration, connectors, managed policies, lifecycle</t>
+  </si>
+  <si>
+    <t>Recording, retrieval, export, and retention, as well as detection and response</t>
+  </si>
+  <si>
+    <t>The model enforces no controls: its output is only a request, and the related requirements fall on the harness.</t>
+  </si>
+  <si>
+    <t>Checkpoints for a Single Tool Invocation</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Checkpoint</t>
+  </si>
+  <si>
+    <t>What Happens</t>
+  </si>
+  <si>
+    <t>Responsible Component</t>
+  </si>
+  <si>
+    <t>Related Requirements</t>
+  </si>
+  <si>
+    <t>Entry authentication</t>
+  </si>
+  <si>
+    <t>Map channel accounts to enterprise identities</t>
+  </si>
+  <si>
+    <t>Interaction channel, identity layer</t>
   </si>
   <si>
     <t>V1.1、V1.2</t>
   </si>
   <si>
-    <t>建立会话</t>
-  </si>
-  <si>
-    <t>签发工作负载身份，确定用户和 Agent</t>
-  </si>
-  <si>
-    <t>Harness、身份层</t>
+    <t>Establish session</t>
+  </si>
+  <si>
+    <t>Issue workload identity; determine user and agent</t>
+  </si>
+  <si>
+    <t>Harness, identity layer</t>
   </si>
   <si>
     <t>V1.4</t>
   </si>
   <si>
-    <t>组装上下文</t>
-  </si>
-  <si>
-    <t>按有效权限过滤工具清单、记忆和检索结果</t>
-  </si>
-  <si>
-    <t>Harness、数据层</t>
+    <t>Assemble context</t>
+  </si>
+  <si>
+    <t>Filter tool list, memory, and retrieval results by effective permissions</t>
+  </si>
+  <si>
+    <t>Harness, data layer</t>
   </si>
   <si>
     <t>V3.3、V8.1、V8.3</t>
   </si>
   <si>
-    <t>前置校验</t>
-  </si>
-  <si>
-    <t>执行前做策略检查和风险分级</t>
-  </si>
-  <si>
-    <t>Harness、策略决策点</t>
+    <t>Pre-invocation validation</t>
+  </si>
+  <si>
+    <t>Policy check and risk classification before execution</t>
+  </si>
+  <si>
+    <t>Harness, policy decision point</t>
   </si>
   <si>
     <t>V2.2、V3.1、V3.2</t>
   </si>
   <si>
-    <t>人工确认</t>
-  </si>
-  <si>
-    <t>按真实参数生成审批，必要时二次认证</t>
+    <t>Human confirmation</t>
+  </si>
+  <si>
+    <t>Generate approval from actual parameters; step-up authentication when necessary</t>
   </si>
   <si>
     <t>V3.4、V3.5</t>
   </si>
   <si>
-    <t>出口执行</t>
-  </si>
-  <si>
-    <t>经网关注入凭证、校验目标、限流</t>
+    <t>Egress execution</t>
+  </si>
+  <si>
+    <t>Inject credentials through the gateway, validate target, rate-limit</t>
   </si>
   <si>
     <t>V4.1、V4.2、V3.8</t>
   </si>
   <si>
-    <t>下游授权判定</t>
-  </si>
-  <si>
-    <t>下游按代表用户访问时传递的用户身份作出授权判定</t>
+    <t>Downstream authorization decision</t>
+  </si>
+  <si>
+    <t>The downstream system makes an authorization decision based on the user identity passed when accessing on behalf of the user</t>
   </si>
   <si>
     <t>V2.1、V4.3、V4.4</t>
   </si>
   <si>
-    <t>处理返回</t>
-  </si>
-  <si>
-    <t>返回内容按不可信处理并标记来源</t>
+    <t>Handle return</t>
+  </si>
+  <si>
+    <t>Treat returned content as untrusted and mark its source</t>
   </si>
   <si>
     <t>V6.1、V6.2</t>
   </si>
   <si>
-    <t>输出检查</t>
-  </si>
-  <si>
-    <t>检查接收方、敏感数据和渲染风险</t>
-  </si>
-  <si>
-    <t>交互渠道、出口网关</t>
+    <t>Output check</t>
+  </si>
+  <si>
+    <t>Check recipient, sensitive data, and rendering risk</t>
+  </si>
+  <si>
+    <t>Interaction channel, egress gateway</t>
   </si>
   <si>
     <t>V7.1、V7.4、V7.5</t>
   </si>
   <si>
-    <t>全程记录</t>
-  </si>
-  <si>
-    <t>每一步写入审计，可追溯到人、Agent 和输入来源</t>
+    <t>Full-process logging</t>
+  </si>
+  <si>
+    <t>Each step is written to audit and traceable to the person, the agent, and the input source</t>
   </si>
   <si>
     <t>V10.1</t>
   </si>
   <si>
-    <t>企业智能体身份与授权安全基线 评估表</t>
-  </si>
-  <si>
-    <t>对应文档</t>
-  </si>
-  <si>
-    <t>企业智能体身份与授权安全基线 v1.0（2026-10-07）。要求的完整上下文、术语、架构图、威胁模型和映射附录都在文档中。</t>
-  </si>
-  <si>
-    <t>文档链接</t>
-  </si>
-  <si>
-    <t>https://github.com/teloa-ai/agent-baseline-assessor/blob/main/01-standard/zh-CN/baseline-v1.0.md</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>共 240 条要求，分布在 62 个小节：L1 90 条，L2 在此基础上增加 137 条，L3 再增加 13 条。</t>
-  </si>
-  <si>
-    <t>评估信息</t>
-  </si>
-  <si>
-    <t>评估对象</t>
-  </si>
-  <si>
-    <t>评估范围</t>
-  </si>
-  <si>
-    <t>评估人</t>
-  </si>
-  <si>
-    <t>评估日期</t>
-  </si>
-  <si>
-    <t>怎么填</t>
-  </si>
-  <si>
-    <t>只填黄色列</t>
-  </si>
-  <si>
-    <t>状态、证据与说明、负责人、计划完成四列由评估者填写，其余列与基线保持一致，不在这里改。</t>
-  </si>
-  <si>
-    <t>下拉选择：未评估、已满足、部分满足、未满足、不适用。整节因适用条件不成立而不适用时，该节每条都选「不适用」。</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>L1 底线，L2 标准，L3 增强；高等级包含低等级的全部要求。达到某级 = 该级及以下的适用要求全部满足。</t>
-  </si>
-  <si>
-    <t>回到网页</t>
-  </si>
-  <si>
-    <t>这份表可以在自评网页的「数据」页导入，状态、证据、负责人和计划完成会按编号回填。</t>
-  </si>
-  <si>
-    <t>两个视角</t>
-  </si>
-  <si>
-    <t>回答「要求什么」。V1 至 V7 沿一次 Agent 行为的发生顺序排列，V8 至 V10 按跨会话持续存在的数据、Agent 和审计组织。</t>
-  </si>
-  <si>
-    <t>回答「在哪里实现」，顺序同基线 4.2 组件表。可按组件筛选后分派给对应团队。组件定义和检查点见「架构视角」页。</t>
+    <t>Enterprise Agent Identity and Authorization Security Baseline Assessment Sheet</t>
+  </si>
+  <si>
+    <t>Source Document</t>
+  </si>
+  <si>
+    <t>Enterprise Agent Identity and Authorization Security Baseline v1.0 (2026-10-07). The document contains the full context of the requirements, terminology, architecture diagrams, threat model, and mapping appendices.</t>
+  </si>
+  <si>
+    <t>Document Link</t>
+  </si>
+  <si>
+    <t>https://github.com/teloa-ai/agent-baseline-assessor/blob/main/01-standard/en/baseline-v1.0.md</t>
+  </si>
+  <si>
+    <t>Contents</t>
+  </si>
+  <si>
+    <t>240 requirements across 62 sections: 90 at L1, 137 more added at L2, and a further 13 added at L3.</t>
+  </si>
+  <si>
+    <t>Assessment Information</t>
+  </si>
+  <si>
+    <t>Assessment Subject</t>
+  </si>
+  <si>
+    <t>Assessment Scope</t>
+  </si>
+  <si>
+    <t>Assessor</t>
+  </si>
+  <si>
+    <t>Assessment Date</t>
+  </si>
+  <si>
+    <t>How to Fill In</t>
+  </si>
+  <si>
+    <t>Fill in only the yellow columns</t>
+  </si>
+  <si>
+    <t>The assessor fills in the four columns Status, Evidence and Notes, Owner, and Planned Completion. The other columns match the baseline and should not be changed here.</t>
+  </si>
+  <si>
+    <t>Select from the drop-down: Not assessed, Met, Partially Met, Unmet, Not applicable. When an entire section does not apply because its applicability condition is not met, select “Not applicable” for every requirement in that section.</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>L1 Baseline, L2 Standard, L3 Enhanced; a higher level includes all requirements of the lower levels. Reaching a level = all applicable requirements at that level and below are met.</t>
+  </si>
+  <si>
+    <t>Back to the Web App</t>
+  </si>
+  <si>
+    <t>This workbook can be imported on the “Data” page of the self-assessment web app; status, evidence, owner, and planned completion are filled back in by ID.</t>
+  </si>
+  <si>
+    <t>Two Perspectives</t>
+  </si>
+  <si>
+    <t>Answers “what is required”. V1 through V7 follow the order in which a single agent action occurs, and V8 through V10 are organized by data, agents, and audit that persist across sessions.</t>
+  </si>
+  <si>
+    <t>Answers “where is it implemented”, in the same order as the component table in section 4.2 of the baseline. Filter by component to assign items to the matching teams. See the “Architecture View” sheet for component definitions and checkpoints.</t>
   </si>
 </sst>
 </file>
@@ -2847,7 +2847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>53</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>55</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>67</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>69</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>71</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>75</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>78</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>81</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>85</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>87</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>89</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>92</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>94</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>100</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>102</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>106</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>108</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>110</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>113</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>117</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>123</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>125</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>127</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>129</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>131</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>133</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>137</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>139</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>141</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>145</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>147</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>149</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>153</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>155</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>157</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>159</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>162</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>164</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>166</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>168</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>170</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>173</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>175</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>178</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>180</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>182</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>184</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>186</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>188</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>191</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>193</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>196</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>198</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>201</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>208</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>210</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>212</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>216</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>218</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>220</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>222</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>224</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>226</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>228</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>231</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>234</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>236</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>238</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>240</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>243</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>245</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>247</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>251</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>253</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>255</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>257</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>261</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>263</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>265</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>267</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>269</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>271</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>274</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>276</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>278</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>281</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>283</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>285</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>287</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>289</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>294</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>296</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>298</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>300</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>304</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>306</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>308</v>
       </c>
@@ -8559,7 +8559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>310</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>314</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>316</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>318</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>320</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>322</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>326</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>328</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>330</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>332</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>335</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>337</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>339</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>341</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>343</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>345</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>349</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>351</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>353</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>355</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>359</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>361</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>363</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>366</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>368</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" ht="90" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>370</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>375</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>379</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>383</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>385</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>387</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>392</v>
       </c>
@@ -10191,7 +10191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>394</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>396</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>398</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>402</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>405</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>409</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>411</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>416</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>418</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>421</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>423</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>425</v>
       </c>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>427</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>431</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>433</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>435</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>440</v>
       </c>
@@ -11055,7 +11055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>442</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>444</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>448</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>450</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>452</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>456</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>458</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>460</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>463</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>465</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>467</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>469</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>472</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>474</v>
       </c>
@@ -11727,7 +11727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>476</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>479</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>481</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>483</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" ht="104" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>485</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" ht="104" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>489</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>497</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>499</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>501</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>515</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>517</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>521</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>524</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>528</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>531</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>533</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>540</v>
       </c>
@@ -13071,7 +13071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>542</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>545</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>551</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>555</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>557</v>
       </c>
@@ -13407,7 +13407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>559</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>561</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>563</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>565</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>568</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>570</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>572</v>
       </c>
@@ -13743,7 +13743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>574</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>577</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>579</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>581</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>584</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" ht="76" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>586</v>
       </c>
@@ -14031,7 +14031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>588</v>
       </c>
@@ -14079,7 +14079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>590</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>592</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>595</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>597</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" ht="62" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>600</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>602</v>
       </c>
@@ -14382,21 +14382,21 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K241">
     <cfRule type="expression" dxfId="3" priority="10">
-      <formula>$K2="已满足"</formula>
+      <formula>$K2="Met"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="11">
-      <formula>$K2="部分满足"</formula>
+      <formula>$K2="Partially Met"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="12">
-      <formula>$K2="未满足"</formula>
+      <formula>$K2="Unmet"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="13">
-      <formula>$K2="不适用"</formula>
+      <formula>$K2="Not applicable"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="状态" error="请从下拉列表中选择" sqref="K2:K241">
-      <formula1>"未评估,已满足,部分满足,未满足,不适用"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Status" error="Please select a value from the drop-down list" sqref="K2:K241">
+      <formula1>"Not assessed,Met,Partially Met,Unmet,Not applicable"</formula1>
     </dataValidation>
   </dataValidations>
   <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -14459,23 +14459,23 @@
         <v>614</v>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1")</f>
         <v>90</v>
       </c>
       <c r="C5" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="D5" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="E5" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="G5" s="10">
@@ -14487,8 +14487,8 @@
         <v>0</v>
       </c>
       <c r="I5" s="10" t="str">
-        <f>IF(C5=B5-F5,"已达到","未达到")</f>
-        <v>未达到</v>
+        <f>IF(C5=B5-F5,"Reached","Not reached")</f>
+        <v>Not reached</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -14496,23 +14496,23 @@
         <v>615</v>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2")</f>
         <v>227</v>
       </c>
       <c r="C6" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="D6" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="E6" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="G6" s="10">
@@ -14524,8 +14524,8 @@
         <v>0</v>
       </c>
       <c r="I6" s="10" t="str">
-        <f>IF(C6=B6-F6,"已达到","未达到")</f>
-        <v>未达到</v>
+        <f>IF(C6=B6-F6,"Reached","Not reached")</f>
+        <v>Not reached</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -14533,23 +14533,23 @@
         <v>616</v>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3")</f>
         <v>240</v>
       </c>
       <c r="C7" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="G7" s="10">
@@ -14561,8 +14561,8 @@
         <v>0</v>
       </c>
       <c r="I7" s="10" t="str">
-        <f>IF(C7=B7-F7,"已达到","未达到")</f>
-        <v>未达到</v>
+        <f>IF(C7=B7-F7,"Reached","Not reached")</f>
+        <v>Not reached</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -14627,15 +14627,15 @@
         <v>18</v>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>7</v>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>12</v>
       </c>
       <c r="D14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>3</v>
       </c>
       <c r="E14" s="10">
@@ -14643,23 +14643,23 @@
         <v>22</v>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>19</v>
       </c>
       <c r="G14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K14" s="10">
@@ -14671,8 +14671,8 @@
         <v>0</v>
       </c>
       <c r="M14" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -14680,15 +14680,15 @@
         <v>32</v>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>8</v>
       </c>
       <c r="C15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>10</v>
       </c>
       <c r="D15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E15" s="10">
@@ -14696,23 +14696,23 @@
         <v>18</v>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>18</v>
       </c>
       <c r="G15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K15" s="10">
@@ -14724,8 +14724,8 @@
         <v>0</v>
       </c>
       <c r="M15" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -14733,15 +14733,15 @@
         <v>62</v>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>18</v>
       </c>
       <c r="C16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>28</v>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>2</v>
       </c>
       <c r="E16" s="10">
@@ -14749,23 +14749,23 @@
         <v>48</v>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>46</v>
       </c>
       <c r="G16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J16" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K16" s="10">
@@ -14777,8 +14777,8 @@
         <v>0</v>
       </c>
       <c r="M16" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A16,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A16,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -14786,15 +14786,15 @@
         <v>76</v>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>12</v>
       </c>
       <c r="C17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>12</v>
       </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>5</v>
       </c>
       <c r="E17" s="10">
@@ -14802,23 +14802,23 @@
         <v>29</v>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>24</v>
       </c>
       <c r="G17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J17" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K17" s="10">
@@ -14830,8 +14830,8 @@
         <v>0</v>
       </c>
       <c r="M17" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A17,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A17,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -14839,15 +14839,15 @@
         <v>65</v>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>16</v>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>16</v>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E18" s="10">
@@ -14855,23 +14855,23 @@
         <v>32</v>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>32</v>
       </c>
       <c r="G18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J18" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K18" s="10">
@@ -14883,8 +14883,8 @@
         <v>0</v>
       </c>
       <c r="M18" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A18,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A18,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -14892,15 +14892,15 @@
         <v>51</v>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>2</v>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>2</v>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E19" s="10">
@@ -14908,23 +14908,23 @@
         <v>4</v>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>4</v>
       </c>
       <c r="G19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J19" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K19" s="10">
@@ -14936,8 +14936,8 @@
         <v>0</v>
       </c>
       <c r="M19" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A19,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A19,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -14945,15 +14945,15 @@
         <v>403</v>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>3</v>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>11</v>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E20" s="10">
@@ -14961,23 +14961,23 @@
         <v>14</v>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>14</v>
       </c>
       <c r="G20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J20" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K20" s="10">
@@ -14989,8 +14989,8 @@
         <v>0</v>
       </c>
       <c r="M20" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A20,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A20,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -14998,15 +14998,15 @@
         <v>232</v>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>7</v>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>6</v>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E21" s="10">
@@ -15014,23 +15014,23 @@
         <v>13</v>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>13</v>
       </c>
       <c r="G21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J21" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K21" s="10">
@@ -15042,8 +15042,8 @@
         <v>0</v>
       </c>
       <c r="M21" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A21,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A21,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -15051,15 +15051,15 @@
         <v>111</v>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>13</v>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>26</v>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E22" s="10">
@@ -15067,23 +15067,23 @@
         <v>40</v>
       </c>
       <c r="F22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>39</v>
       </c>
       <c r="G22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J22" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K22" s="10">
@@ -15095,8 +15095,8 @@
         <v>0</v>
       </c>
       <c r="M22" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A22,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A22,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -15104,15 +15104,15 @@
         <v>79</v>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>4</v>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>14</v>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>2</v>
       </c>
       <c r="E23" s="10">
@@ -15120,23 +15120,23 @@
         <v>20</v>
       </c>
       <c r="F23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>18</v>
       </c>
       <c r="G23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J23" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K23" s="10">
@@ -15148,8 +15148,8 @@
         <v>0</v>
       </c>
       <c r="M23" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$D$2:$D$241,$A23,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A23,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -15201,8 +15201,8 @@
         <v>0</v>
       </c>
       <c r="M24" s="17" t="str">
-        <f>IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -15256,15 +15256,15 @@
         <v>16</v>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>11</v>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>11</v>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E29" s="10">
@@ -15272,23 +15272,23 @@
         <v>23</v>
       </c>
       <c r="F29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>22</v>
       </c>
       <c r="G29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K29" s="10">
@@ -15300,8 +15300,8 @@
         <v>0</v>
       </c>
       <c r="M29" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A29,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A29,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -15309,15 +15309,15 @@
         <v>82</v>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>11</v>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>14</v>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>3</v>
       </c>
       <c r="E30" s="10">
@@ -15325,23 +15325,23 @@
         <v>28</v>
       </c>
       <c r="F30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>25</v>
       </c>
       <c r="G30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J30" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K30" s="10">
@@ -15353,8 +15353,8 @@
         <v>0</v>
       </c>
       <c r="M30" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A30,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A30,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -15362,15 +15362,15 @@
         <v>150</v>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>9</v>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>16</v>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>2</v>
       </c>
       <c r="E31" s="10">
@@ -15378,23 +15378,23 @@
         <v>27</v>
       </c>
       <c r="F31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>25</v>
       </c>
       <c r="G31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J31" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K31" s="10">
@@ -15406,8 +15406,8 @@
         <v>0</v>
       </c>
       <c r="M31" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A31,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A31,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -15415,15 +15415,15 @@
         <v>213</v>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>14</v>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>18</v>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E32" s="10">
@@ -15431,23 +15431,23 @@
         <v>33</v>
       </c>
       <c r="F32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>32</v>
       </c>
       <c r="G32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J32" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K32" s="10">
@@ -15459,8 +15459,8 @@
         <v>0</v>
       </c>
       <c r="M32" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A32,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A32,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -15468,15 +15468,15 @@
         <v>290</v>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>16</v>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>11</v>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E33" s="10">
@@ -15484,23 +15484,23 @@
         <v>27</v>
       </c>
       <c r="F33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>27</v>
       </c>
       <c r="G33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J33" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K33" s="10">
@@ -15512,8 +15512,8 @@
         <v>0</v>
       </c>
       <c r="M33" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A33,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A33,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -15521,15 +15521,15 @@
         <v>356</v>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>4</v>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>8</v>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E34" s="10">
@@ -15537,23 +15537,23 @@
         <v>13</v>
       </c>
       <c r="F34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>12</v>
       </c>
       <c r="G34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J34" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K34" s="10">
@@ -15565,8 +15565,8 @@
         <v>0</v>
       </c>
       <c r="M34" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A34,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A34,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -15574,15 +15574,15 @@
         <v>388</v>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>6</v>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>12</v>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
       <c r="E35" s="10">
@@ -15590,23 +15590,23 @@
         <v>18</v>
       </c>
       <c r="F35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>18</v>
       </c>
       <c r="G35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J35" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K35" s="10">
@@ -15618,8 +15618,8 @@
         <v>0</v>
       </c>
       <c r="M35" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A35,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A35,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -15627,15 +15627,15 @@
         <v>436</v>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>5</v>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>16</v>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E36" s="10">
@@ -15643,23 +15643,23 @@
         <v>22</v>
       </c>
       <c r="F36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>21</v>
       </c>
       <c r="G36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J36" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K36" s="10">
@@ -15671,8 +15671,8 @@
         <v>0</v>
       </c>
       <c r="M36" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A36,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A36,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -15680,15 +15680,15 @@
         <v>492</v>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>9</v>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>16</v>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
       <c r="E37" s="10">
@@ -15696,23 +15696,23 @@
         <v>26</v>
       </c>
       <c r="F37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>25</v>
       </c>
       <c r="G37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J37" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K37" s="10">
@@ -15724,8 +15724,8 @@
         <v>0</v>
       </c>
       <c r="M37" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A37,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A37,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -15733,15 +15733,15 @@
         <v>552</v>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>5</v>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>15</v>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>3</v>
       </c>
       <c r="E38" s="10">
@@ -15749,23 +15749,23 @@
         <v>23</v>
       </c>
       <c r="F38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)))</f>
         <v>20</v>
       </c>
       <c r="G38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"已满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Met")</f>
         <v>0</v>
       </c>
       <c r="H38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"部分满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Partially Met")</f>
         <v>0</v>
       </c>
       <c r="I38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"未满足")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Unmet")</f>
         <v>0</v>
       </c>
       <c r="J38" s="10">
-        <f>COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'评估表'!$K$2:$K$241,"不适用")</f>
+        <f>COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;="&amp;VALUE(RIGHT($B$10,1)),'Assessment Sheet'!$K$2:$K$241,"Not applicable")</f>
         <v>0</v>
       </c>
       <c r="K38" s="10">
@@ -15777,8 +15777,8 @@
         <v>0</v>
       </c>
       <c r="M38" s="10" t="str">
-        <f>IF(COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$B$2:$B$241,$A38,'评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$B$2:$B$241,$A38,'Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -15830,8 +15830,8 @@
         <v>0</v>
       </c>
       <c r="M39" s="17" t="str">
-        <f>IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=1",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"未达 L1",IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=2",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L1",IF(COUNTIFS('评估表'!$O$2:$O$241,"&lt;=3",'评估表'!$K$2:$K$241,"&lt;&gt;已满足",'评估表'!$K$2:$K$241,"&lt;&gt;不适用")&gt;0,"L2","L3")))</f>
-        <v>未达 L1</v>
+        <f>IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=1",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"Below L1",IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=2",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L1",IF(COUNTIFS('Assessment Sheet'!$O$2:$O$241,"&lt;=3",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Met",'Assessment Sheet'!$K$2:$K$241,"&lt;&gt;Not applicable")&gt;0,"L2","L3")))</f>
+        <v>Below L1</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
@@ -15882,43 +15882,43 @@
         <v>18</v>
       </c>
       <c r="B44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>12</v>
       </c>
       <c r="C44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>3</v>
       </c>
       <c r="D44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>1</v>
       </c>
       <c r="E44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>4</v>
       </c>
       <c r="F44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>1</v>
       </c>
       <c r="G44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>0</v>
       </c>
       <c r="J44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>1</v>
       </c>
       <c r="K44" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A44,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A44,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L44" s="10">
@@ -15931,43 +15931,43 @@
         <v>32</v>
       </c>
       <c r="B45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>6</v>
       </c>
       <c r="C45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>1</v>
       </c>
       <c r="D45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>0</v>
       </c>
       <c r="E45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>0</v>
       </c>
       <c r="F45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>0</v>
       </c>
       <c r="G45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>10</v>
       </c>
       <c r="I45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>1</v>
       </c>
       <c r="J45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K45" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A45,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A45,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L45" s="10">
@@ -15980,43 +15980,43 @@
         <v>62</v>
       </c>
       <c r="B46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>1</v>
       </c>
       <c r="C46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>2</v>
       </c>
       <c r="D46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>14</v>
       </c>
       <c r="E46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>2</v>
       </c>
       <c r="F46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>11</v>
       </c>
       <c r="G46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>10</v>
       </c>
       <c r="H46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>4</v>
       </c>
       <c r="I46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>3</v>
       </c>
       <c r="J46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K46" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A46,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A46,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>1</v>
       </c>
       <c r="L46" s="10">
@@ -16029,43 +16029,43 @@
         <v>76</v>
       </c>
       <c r="B47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>1</v>
       </c>
       <c r="C47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>15</v>
       </c>
       <c r="D47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>8</v>
       </c>
       <c r="E47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>0</v>
       </c>
       <c r="F47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>0</v>
       </c>
       <c r="G47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>1</v>
       </c>
       <c r="J47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>1</v>
       </c>
       <c r="K47" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A47,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A47,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>3</v>
       </c>
       <c r="L47" s="10">
@@ -16078,43 +16078,43 @@
         <v>65</v>
       </c>
       <c r="B48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>1</v>
       </c>
       <c r="C48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>2</v>
       </c>
       <c r="D48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>2</v>
       </c>
       <c r="E48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>19</v>
       </c>
       <c r="F48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>2</v>
       </c>
       <c r="G48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>3</v>
       </c>
       <c r="I48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>3</v>
       </c>
       <c r="J48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K48" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A48,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A48,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L48" s="10">
@@ -16127,43 +16127,43 @@
         <v>51</v>
       </c>
       <c r="B49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>1</v>
       </c>
       <c r="C49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>0</v>
       </c>
       <c r="D49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>0</v>
       </c>
       <c r="E49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>3</v>
       </c>
       <c r="F49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>0</v>
       </c>
       <c r="G49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>0</v>
       </c>
       <c r="J49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K49" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A49,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A49,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L49" s="10">
@@ -16176,43 +16176,43 @@
         <v>403</v>
       </c>
       <c r="B50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>0</v>
       </c>
       <c r="C50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>0</v>
       </c>
       <c r="D50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>0</v>
       </c>
       <c r="E50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>0</v>
       </c>
       <c r="F50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>0</v>
       </c>
       <c r="G50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>1</v>
       </c>
       <c r="I50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>13</v>
       </c>
       <c r="J50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K50" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A50,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A50,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L50" s="10">
@@ -16225,43 +16225,43 @@
         <v>232</v>
       </c>
       <c r="B51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>0</v>
       </c>
       <c r="C51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>0</v>
       </c>
       <c r="D51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>0</v>
       </c>
       <c r="E51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>3</v>
       </c>
       <c r="F51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>10</v>
       </c>
       <c r="G51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>0</v>
       </c>
       <c r="J51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>0</v>
       </c>
       <c r="K51" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A51,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A51,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>0</v>
       </c>
       <c r="L51" s="10">
@@ -16274,43 +16274,43 @@
         <v>111</v>
       </c>
       <c r="B52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>0</v>
       </c>
       <c r="C52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>3</v>
       </c>
       <c r="D52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>2</v>
       </c>
       <c r="E52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>2</v>
       </c>
       <c r="F52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>3</v>
       </c>
       <c r="G52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>3</v>
       </c>
       <c r="H52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>1</v>
       </c>
       <c r="J52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>22</v>
       </c>
       <c r="K52" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A52,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A52,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>4</v>
       </c>
       <c r="L52" s="10">
@@ -16323,43 +16323,43 @@
         <v>79</v>
       </c>
       <c r="B53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V1 身份与认证")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V1 Identity and Authentication")</f>
         <v>1</v>
       </c>
       <c r="C53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V2 委托与有效权限")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V2 Delegation and Effective Permissions")</f>
         <v>2</v>
       </c>
       <c r="D53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V3 授权决策")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V3 Authorization Decisions")</f>
         <v>0</v>
       </c>
       <c r="E53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V4 凭证与出口执行")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V4 Credentials and Egress Enforcement")</f>
         <v>0</v>
       </c>
       <c r="F53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V5 执行隔离")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V5 Execution Isolation")</f>
         <v>0</v>
       </c>
       <c r="G53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V6 上下文与不可信输入")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V6 Context and Untrusted Input")</f>
         <v>0</v>
       </c>
       <c r="H53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V7 输出与可见性")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V7 Output and Visibility")</f>
         <v>0</v>
       </c>
       <c r="I53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V8 数据、记忆与产出物")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V8 Data, Memory, and Output Artifacts")</f>
         <v>0</v>
       </c>
       <c r="J53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V9 生命周期与治理")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V9 Lifecycle and Governance")</f>
         <v>2</v>
       </c>
       <c r="K53" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A53,'评估表'!$B$2:$B$241,"V10 审计、检测与响应")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A53,'Assessment Sheet'!$B$2:$B$241,"V10 Audit, Detection, and Response")</f>
         <v>15</v>
       </c>
       <c r="L53" s="10">
@@ -16498,7 +16498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -16556,7 +16556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -16672,7 +16672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
@@ -16730,7 +16730,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>61</v>
       </c>
@@ -16759,7 +16759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>64</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>75</v>
       </c>
@@ -16817,7 +16817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>81</v>
       </c>
@@ -16846,7 +16846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>85</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>92</v>
       </c>
@@ -16933,7 +16933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>102</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>106</v>
       </c>
@@ -16991,7 +16991,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>108</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>117</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>123</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>141</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>145</v>
       </c>
@@ -17136,7 +17136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>149</v>
       </c>
@@ -17165,7 +17165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>153</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
@@ -17223,7 +17223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>159</v>
       </c>
@@ -17252,7 +17252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>166</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>175</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>178</v>
       </c>
@@ -17339,7 +17339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>180</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>198</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>212</v>
       </c>
@@ -17426,7 +17426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>216</v>
       </c>
@@ -17455,7 +17455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>228</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>231</v>
       </c>
@@ -17513,7 +17513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>234</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>238</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>240</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>247</v>
       </c>
@@ -17629,7 +17629,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>251</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>267</v>
       </c>
@@ -17687,7 +17687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>276</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>278</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>281</v>
       </c>
@@ -17774,7 +17774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>283</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>289</v>
       </c>
@@ -17832,7 +17832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>294</v>
       </c>
@@ -17861,7 +17861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>300</v>
       </c>
@@ -17890,7 +17890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>304</v>
       </c>
@@ -17919,7 +17919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>310</v>
       </c>
@@ -17948,7 +17948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>314</v>
       </c>
@@ -17977,7 +17977,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>320</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>322</v>
       </c>
@@ -18035,7 +18035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>326</v>
       </c>
@@ -18064,7 +18064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>328</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>330</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>332</v>
       </c>
@@ -18151,7 +18151,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>335</v>
       </c>
@@ -18180,7 +18180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>339</v>
       </c>
@@ -18209,7 +18209,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>341</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>345</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>355</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>363</v>
       </c>
@@ -18354,7 +18354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -18383,7 +18383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>387</v>
       </c>
@@ -18412,7 +18412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>392</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>398</v>
       </c>
@@ -18470,7 +18470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>411</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>425</v>
       </c>
@@ -18557,7 +18557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>435</v>
       </c>
@@ -18586,7 +18586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>440</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>444</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>448</v>
       </c>
@@ -18673,7 +18673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>456</v>
       </c>
@@ -18731,7 +18731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>497</v>
       </c>
@@ -18760,7 +18760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>501</v>
       </c>
@@ -18789,7 +18789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>517</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>540</v>
       </c>
@@ -18905,7 +18905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>542</v>
       </c>
@@ -18934,7 +18934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>545</v>
       </c>
@@ -18963,7 +18963,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>551</v>
       </c>
@@ -18992,7 +18992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>555</v>
       </c>
@@ -19021,7 +19021,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>565</v>
       </c>
@@ -19050,7 +19050,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>581</v>
       </c>
@@ -19079,7 +19079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>586</v>
       </c>
@@ -19108,7 +19108,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>24</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>26</v>
       </c>
@@ -19166,7 +19166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>37</v>
       </c>
@@ -19195,7 +19195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>39</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>41</v>
       </c>
@@ -19253,7 +19253,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>50</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>53</v>
       </c>
@@ -19311,7 +19311,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>55</v>
       </c>
@@ -19340,7 +19340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>67</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>71</v>
       </c>
@@ -19398,7 +19398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>78</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>87</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" ht="90" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>94</v>
       </c>
@@ -19485,7 +19485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>96</v>
       </c>
@@ -19514,7 +19514,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>98</v>
       </c>
@@ -19543,7 +19543,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="109" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>110</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>113</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>115</v>
       </c>
@@ -19630,7 +19630,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>121</v>
       </c>
@@ -19659,7 +19659,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>125</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>127</v>
       </c>
@@ -19717,7 +19717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>129</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>133</v>
       </c>
@@ -19775,7 +19775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>137</v>
       </c>
@@ -19804,7 +19804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>147</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>157</v>
       </c>
@@ -19862,7 +19862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>162</v>
       </c>
@@ -19891,7 +19891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="121" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>164</v>
       </c>
@@ -19920,7 +19920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>170</v>
       </c>
@@ -19949,7 +19949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>173</v>
       </c>
@@ -19978,7 +19978,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>182</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>184</v>
       </c>
@@ -20036,7 +20036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>186</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>188</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>193</v>
       </c>
@@ -20123,7 +20123,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>196</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>201</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>203</v>
       </c>
@@ -20210,7 +20210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>206</v>
       </c>
@@ -20239,7 +20239,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>208</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>210</v>
       </c>
@@ -20297,7 +20297,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>218</v>
       </c>
@@ -20326,7 +20326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>220</v>
       </c>
@@ -20355,7 +20355,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>222</v>
       </c>
@@ -20384,7 +20384,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>224</v>
       </c>
@@ -20413,7 +20413,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>226</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>236</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>243</v>
       </c>
@@ -20500,7 +20500,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>245</v>
       </c>
@@ -20529,7 +20529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>253</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>255</v>
       </c>
@@ -20587,7 +20587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>257</v>
       </c>
@@ -20616,7 +20616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>261</v>
       </c>
@@ -20645,7 +20645,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>263</v>
       </c>
@@ -20674,7 +20674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" ht="76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>269</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>271</v>
       </c>
@@ -20732,7 +20732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>274</v>
       </c>
@@ -20761,7 +20761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="151" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>285</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>287</v>
       </c>
@@ -20819,7 +20819,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>296</v>
       </c>
@@ -20848,7 +20848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>298</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>306</v>
       </c>
@@ -20906,7 +20906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>308</v>
       </c>
@@ -20935,7 +20935,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>316</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>318</v>
       </c>
@@ -20993,7 +20993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>337</v>
       </c>
@@ -21022,7 +21022,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>343</v>
       </c>
@@ -21051,7 +21051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>349</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>351</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>353</v>
       </c>
@@ -21138,7 +21138,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>359</v>
       </c>
@@ -21167,7 +21167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>361</v>
       </c>
@@ -21196,7 +21196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>366</v>
       </c>
@@ -21225,7 +21225,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>368</v>
       </c>
@@ -21283,7 +21283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>379</v>
       </c>
@@ -21312,7 +21312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>383</v>
       </c>
@@ -21341,7 +21341,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>385</v>
       </c>
@@ -21370,7 +21370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>394</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>396</v>
       </c>
@@ -21428,7 +21428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>402</v>
       </c>
@@ -21457,7 +21457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>405</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>409</v>
       </c>
@@ -21515,7 +21515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>416</v>
       </c>
@@ -21544,7 +21544,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>418</v>
       </c>
@@ -21573,7 +21573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>421</v>
       </c>
@@ -21602,7 +21602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>423</v>
       </c>
@@ -21631,7 +21631,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>427</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>431</v>
       </c>
@@ -21689,7 +21689,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>433</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="184" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>442</v>
       </c>
@@ -21747,7 +21747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="185" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>450</v>
       </c>
@@ -21776,7 +21776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>452</v>
       </c>
@@ -21805,7 +21805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>458</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>460</v>
       </c>
@@ -21863,7 +21863,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>463</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>465</v>
       </c>
@@ -21921,7 +21921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>467</v>
       </c>
@@ -21950,7 +21950,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>469</v>
       </c>
@@ -21979,7 +21979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="193" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>472</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>476</v>
       </c>
@@ -22037,7 +22037,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>479</v>
       </c>
@@ -22066,7 +22066,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>481</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>483</v>
       </c>
@@ -22124,7 +22124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>485</v>
       </c>
@@ -22153,7 +22153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>489</v>
       </c>
@@ -22211,7 +22211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>499</v>
       </c>
@@ -22385,7 +22385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>515</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>521</v>
       </c>
@@ -22472,7 +22472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>524</v>
       </c>
@@ -22530,7 +22530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>528</v>
       </c>
@@ -22559,7 +22559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>531</v>
       </c>
@@ -22646,7 +22646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>557</v>
       </c>
@@ -22675,7 +22675,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>559</v>
       </c>
@@ -22704,7 +22704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>561</v>
       </c>
@@ -22733,7 +22733,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>568</v>
       </c>
@@ -22762,7 +22762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>570</v>
       </c>
@@ -22791,7 +22791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>572</v>
       </c>
@@ -22820,7 +22820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>574</v>
       </c>
@@ -22849,7 +22849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>577</v>
       </c>
@@ -22878,7 +22878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>584</v>
       </c>
@@ -22907,7 +22907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>588</v>
       </c>
@@ -22936,7 +22936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="226" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>590</v>
       </c>
@@ -22965,7 +22965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>592</v>
       </c>
@@ -22994,7 +22994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="228" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>595</v>
       </c>
@@ -23023,7 +23023,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="229" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>597</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" ht="62" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>600</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
@@ -23150,19 +23150,19 @@
         <v>647</v>
       </c>
       <c r="E6" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A6,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A6,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>7</v>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A6,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A6,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>12</v>
       </c>
       <c r="G6" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A6,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A6,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="62" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -23174,19 +23174,19 @@
         <v>649</v>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A7,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A7,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>8</v>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A7,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A7,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>10</v>
       </c>
       <c r="G7" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A7,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A7,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>62</v>
       </c>
@@ -23198,19 +23198,19 @@
         <v>651</v>
       </c>
       <c r="E8" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A8,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A8,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>18</v>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A8,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A8,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>28</v>
       </c>
       <c r="G8" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A8,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A8,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>76</v>
       </c>
@@ -23222,19 +23222,19 @@
         <v>647</v>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A9,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A9,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>12</v>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A9,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A9,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>12</v>
       </c>
       <c r="G9" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A9,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A9,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>65</v>
       </c>
@@ -23246,19 +23246,19 @@
         <v>647</v>
       </c>
       <c r="E10" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A10,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A10,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>16</v>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A10,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A10,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>16</v>
       </c>
       <c r="G10" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A10,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A10,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>51</v>
       </c>
@@ -23270,19 +23270,19 @@
         <v>655</v>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A11,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A11,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>2</v>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A11,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A11,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>2</v>
       </c>
       <c r="G11" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A11,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A11,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>403</v>
       </c>
@@ -23294,19 +23294,19 @@
         <v>657</v>
       </c>
       <c r="E12" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A12,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A12,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>3</v>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A12,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A12,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>11</v>
       </c>
       <c r="G12" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A12,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A12,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>232</v>
       </c>
@@ -23318,19 +23318,19 @@
         <v>659</v>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A13,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A13,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>7</v>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A13,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A13,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>6</v>
       </c>
       <c r="G13" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A13,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A13,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>111</v>
       </c>
@@ -23342,19 +23342,19 @@
         <v>647</v>
       </c>
       <c r="E14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>13</v>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>26</v>
       </c>
       <c r="G14" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A14,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A14,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>79</v>
       </c>
@@ -23366,15 +23366,15 @@
         <v>647</v>
       </c>
       <c r="E15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L1")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L1")</f>
         <v>4</v>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L2")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L2")</f>
         <v>14</v>
       </c>
       <c r="G15" s="10">
-        <f>COUNTIFS('评估表'!$D$2:$D$241,$A15,'评估表'!$F$2:$F$241,"L3")</f>
+        <f>COUNTIFS('Assessment Sheet'!$D$2:$D$241,$A15,'Assessment Sheet'!$F$2:$F$241,"L3")</f>
         <v>2</v>
       </c>
     </row>
@@ -23407,7 +23407,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>1</v>
       </c>
@@ -23426,7 +23426,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>2</v>
       </c>
@@ -23445,7 +23445,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>3</v>
       </c>
@@ -23464,7 +23464,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>4</v>
       </c>
@@ -23483,7 +23483,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>5</v>
       </c>
@@ -23502,7 +23502,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>6</v>
       </c>
@@ -23521,7 +23521,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" ht="62" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>7</v>
       </c>
@@ -23540,7 +23540,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>8</v>
       </c>
@@ -23559,7 +23559,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>9</v>
       </c>
@@ -23578,7 +23578,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>10</v>
       </c>
@@ -23643,7 +23643,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>705</v>
       </c>
@@ -23659,7 +23659,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>709</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>717</v>
       </c>
@@ -23735,7 +23735,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>10</v>
       </c>
@@ -23751,7 +23751,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>722</v>
       </c>
@@ -23777,7 +23777,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>3</v>
       </c>
